--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_C_MCBW-CSTD-0-01-B-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_C_MCBW-CSTD-0-01-B-C0.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\10_Development\840B\10_設計\ファイル名変更のみ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Work\BEV\BEV設計・実装\課題管理一覧\フレーム変更漏れ対応\Alertパラメータ設計書\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F2EFA3-BF18-43AF-A541-98E2D94DE90A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="25296" windowHeight="9492"/>
+    <workbookView xWindow="25974" yWindow="-109" windowWidth="26301" windowHeight="14305" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙" sheetId="1" r:id="rId1"/>
@@ -21,17 +22,30 @@
     <sheet name="Reference" sheetId="3" r:id="rId7"/>
     <sheet name="History" sheetId="7" r:id="rId8"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>YOSHIKI IWATA</author>
   </authors>
   <commentList>
-    <comment ref="B10" authorId="0" shapeId="0">
+    <comment ref="B10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000001000000}">
       <text>
         <r>
           <rPr>
@@ -48,7 +62,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C12" authorId="0" shapeId="0">
+    <comment ref="C12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000002000000}">
       <text>
         <r>
           <rPr>
@@ -65,7 +79,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E12" authorId="0" shapeId="0">
+    <comment ref="E12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0200-000003000000}">
       <text>
         <r>
           <rPr>
@@ -85,12 +99,12 @@
 </file>
 
 <file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>鈴木　大助</author>
   </authors>
   <commentList>
-    <comment ref="C3" authorId="0" shapeId="0">
+    <comment ref="C3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000001000000}">
       <text>
         <r>
           <rPr>
@@ -136,7 +150,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P3" authorId="0" shapeId="0">
+    <comment ref="P3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000002000000}">
       <text>
         <r>
           <rPr>
@@ -152,7 +166,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q3" authorId="0" shapeId="0">
+    <comment ref="Q3" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000003000000}">
       <text>
         <r>
           <rPr>
@@ -170,7 +184,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="P33" authorId="0" shapeId="0">
+    <comment ref="P33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000004000000}">
       <text>
         <r>
           <rPr>
@@ -186,7 +200,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="Q33" authorId="0" shapeId="0">
+    <comment ref="Q33" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0300-000005000000}">
       <text>
         <r>
           <rPr>
@@ -207,13 +221,13 @@
 </file>
 
 <file path=xl/comments3.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>鈴木　大助</author>
     <author>YOSHIKI IWATA</author>
   </authors>
   <commentList>
-    <comment ref="E2" authorId="0" shapeId="0">
+    <comment ref="E2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000001000000}">
       <text>
         <r>
           <rPr>
@@ -228,7 +242,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F2" authorId="1" shapeId="0">
+    <comment ref="F2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000002000000}">
       <text>
         <r>
           <rPr>
@@ -256,7 +270,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G2" authorId="0" shapeId="0">
+    <comment ref="G2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000003000000}">
       <text>
         <r>
           <rPr>
@@ -271,7 +285,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H2" authorId="0" shapeId="0">
+    <comment ref="H2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000004000000}">
       <text>
         <r>
           <rPr>
@@ -292,7 +306,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I2" authorId="0" shapeId="0">
+    <comment ref="I2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000005000000}">
       <text>
         <r>
           <rPr>
@@ -307,7 +321,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J2" authorId="1" shapeId="0">
+    <comment ref="J2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000006000000}">
       <text>
         <r>
           <rPr>
@@ -323,7 +337,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="K2" authorId="0" shapeId="0">
+    <comment ref="K2" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0400-000007000000}">
       <text>
         <r>
           <rPr>
@@ -339,7 +353,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="L2" authorId="1" shapeId="0">
+    <comment ref="L2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000008000000}">
       <text>
         <r>
           <rPr>
@@ -354,7 +368,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="M2" authorId="1" shapeId="0">
+    <comment ref="M2" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0400-000009000000}">
       <text>
         <r>
           <rPr>
@@ -374,13 +388,13 @@
 </file>
 
 <file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>YOSHIKI IWATA</author>
     <author>鈴木　大助</author>
   </authors>
   <commentList>
-    <comment ref="B6" authorId="0" shapeId="0">
+    <comment ref="B6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0600-000001000000}">
       <text>
         <r>
           <rPr>
@@ -397,7 +411,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="C9" authorId="1" shapeId="0">
+    <comment ref="C9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0600-000002000000}">
       <text>
         <r>
           <rPr>
@@ -413,7 +427,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E9" authorId="1" shapeId="0">
+    <comment ref="E9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0600-000003000000}">
       <text>
         <r>
           <rPr>
@@ -429,7 +443,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F9" authorId="1" shapeId="0">
+    <comment ref="F9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0600-000004000000}">
       <text>
         <r>
           <rPr>
@@ -444,7 +458,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G9" authorId="1" shapeId="0">
+    <comment ref="G9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0600-000005000000}">
       <text>
         <r>
           <rPr>
@@ -460,7 +474,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H9" authorId="1" shapeId="0">
+    <comment ref="H9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0600-000006000000}">
       <text>
         <r>
           <rPr>
@@ -476,7 +490,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I9" authorId="1" shapeId="0">
+    <comment ref="I9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0600-000007000000}">
       <text>
         <r>
           <rPr>
@@ -492,7 +506,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J9" authorId="1" shapeId="0">
+    <comment ref="J9" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0600-000008000000}">
       <text>
         <r>
           <rPr>
@@ -512,7 +526,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2565" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2565" uniqueCount="297">
   <si>
     <t>更新履歴</t>
     <phoneticPr fontId="2"/>
@@ -2513,10 +2527,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>VSC1S95</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
     <t>RWT_EN</t>
     <phoneticPr fontId="2"/>
   </si>
@@ -2542,10 +2552,6 @@
   </si>
   <si>
     <t>BAT_AO</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>VSC1S95_STS</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -2659,10 +2665,6 @@
   </si>
   <si>
     <t>C_MCBW-CSTD-0-MEF01-REQ02-</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>VSC1S95_STS</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -3025,11 +3027,19 @@
     </rPh>
     <phoneticPr fontId="2"/>
   </si>
+  <si>
+    <t>DDM1S17_STS</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>DDM1S17</t>
+    <phoneticPr fontId="2"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="22">
     <font>
       <sz val="11"/>
@@ -5176,16 +5186,37 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="56" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="19" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -5230,31 +5261,10 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="18" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="68" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="50" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="69" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="61" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="19" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
@@ -5313,77 +5323,7 @@
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="18">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="0" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="7">
     <dxf>
       <fill>
         <patternFill>
@@ -5440,16 +5380,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFFFF00"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -5494,7 +5424,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="2" name="正方形/長方形 1"/>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0500-000002000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6272,18 +6208,24 @@
     <xdr:from>
       <xdr:col>21</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>91</xdr:row>
+      <xdr:row>42</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>43</xdr:col>
-      <xdr:colOff>237403</xdr:colOff>
-      <xdr:row>98</xdr:row>
-      <xdr:rowOff>45823</xdr:rowOff>
+      <xdr:colOff>344092</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>115723</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="11" name="図 10" descr="画面の領域"/>
+        <xdr:cNvPr id="10" name="図 9" descr="画面の領域">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00000A000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -6302,8 +6244,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15697200" y="15708086"/>
-          <a:ext cx="13648603" cy="1188823"/>
+          <a:off x="15697200" y="9666514"/>
+          <a:ext cx="13755292" cy="3871295"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6316,18 +6258,24 @@
     <xdr:from>
       <xdr:col>21</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
+      <xdr:row>91</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>43</xdr:col>
-      <xdr:colOff>344092</xdr:colOff>
-      <xdr:row>65</xdr:row>
-      <xdr:rowOff>115723</xdr:rowOff>
+      <xdr:colOff>237403</xdr:colOff>
+      <xdr:row>98</xdr:row>
+      <xdr:rowOff>45823</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="10" name="図 9" descr="画面の領域"/>
+        <xdr:cNvPr id="11" name="図 10" descr="画面の領域">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00000B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -6346,8 +6294,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="15697200" y="9666514"/>
-          <a:ext cx="13755292" cy="3871295"/>
+          <a:off x="15697200" y="15708086"/>
+          <a:ext cx="13648603" cy="1188823"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -6371,7 +6319,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="20" name="線吹き出し 1 (枠付き) 19"/>
+        <xdr:cNvPr id="20" name="線吹き出し 1 (枠付き) 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000014000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6468,7 +6422,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="23" name="線吹き出し 1 (枠付き) 22"/>
+        <xdr:cNvPr id="23" name="線吹き出し 1 (枠付き) 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000017000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6587,7 +6547,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="28" name="正方形/長方形 27"/>
+        <xdr:cNvPr id="28" name="正方形/長方形 27">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00001C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6647,7 +6613,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="29" name="正方形/長方形 28"/>
+        <xdr:cNvPr id="29" name="正方形/長方形 28">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00001D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6707,7 +6679,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="30" name="正方形/長方形 29"/>
+        <xdr:cNvPr id="30" name="正方形/長方形 29">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00001E000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6767,7 +6745,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="32" name="線吹き出し 1 (枠付き) 31"/>
+        <xdr:cNvPr id="32" name="線吹き出し 1 (枠付き) 31">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000020000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6853,7 +6837,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="33" name="正方形/長方形 32"/>
+        <xdr:cNvPr id="33" name="正方形/長方形 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000021000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -6913,7 +6903,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="34" name="線吹き出し 1 (枠付き) 33"/>
+        <xdr:cNvPr id="34" name="線吹き出し 1 (枠付き) 33">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000022000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7143,7 +7139,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="44" name="線吹き出し 1 (枠付き) 43"/>
+        <xdr:cNvPr id="44" name="線吹き出し 1 (枠付き) 43">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00002C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7270,7 +7272,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="45" name="線吹き出し 1 (枠付き) 44"/>
+        <xdr:cNvPr id="45" name="線吹き出し 1 (枠付き) 44">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00002D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7353,7 +7361,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="51" name="線吹き出し 1 (枠付き) 50"/>
+        <xdr:cNvPr id="51" name="線吹き出し 1 (枠付き) 50">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000033000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7448,7 +7462,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="54" name="線吹き出し 1 (枠付き) 53"/>
+        <xdr:cNvPr id="54" name="線吹き出し 1 (枠付き) 53">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000036000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7556,7 +7576,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="55" name="正方形/長方形 54"/>
+        <xdr:cNvPr id="55" name="正方形/長方形 54">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000037000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7616,7 +7642,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="56" name="正方形/長方形 55"/>
+        <xdr:cNvPr id="56" name="正方形/長方形 55">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000038000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7676,7 +7708,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="57" name="線吹き出し 1 (枠付き) 56"/>
+        <xdr:cNvPr id="57" name="線吹き出し 1 (枠付き) 56">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000039000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7792,7 +7830,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="59" name="正方形/長方形 58"/>
+        <xdr:cNvPr id="59" name="正方形/長方形 58">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00003B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7852,7 +7896,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="60" name="線吹き出し 1 (枠付き) 59"/>
+        <xdr:cNvPr id="60" name="線吹き出し 1 (枠付き) 59">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00003C000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -7935,7 +7985,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="61" name="線吹き出し 1 (枠付き) 60"/>
+        <xdr:cNvPr id="61" name="線吹き出し 1 (枠付き) 60">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00003D000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8032,7 +8088,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="63" name="正方形/長方形 62"/>
+        <xdr:cNvPr id="63" name="正方形/長方形 62">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00003F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8092,7 +8154,13 @@
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="24" name="線吹き出し 1 (枠付き) 23"/>
+        <xdr:cNvPr id="24" name="線吹き出し 1 (枠付き) 23">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000018000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvSpPr/>
       </xdr:nvSpPr>
       <xdr:spPr>
@@ -8229,17 +8297,6 @@
             </a:rPr>
             <a:t>にするために通信途絶ビットを参照しているが、</a:t>
           </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t/>
-          </a:r>
           <a:br>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
               <a:solidFill>
@@ -8294,17 +8351,6 @@
             </a:rPr>
             <a:t>）となり</a:t>
           </a:r>
-          <a:r>
-            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
-              <a:solidFill>
-                <a:sysClr val="windowText" lastClr="000000"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
-            </a:rPr>
-            <a:t/>
-          </a:r>
           <a:br>
             <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
               <a:solidFill>
@@ -8357,7 +8403,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2" descr="画面の領域"/>
+        <xdr:cNvPr id="3" name="図 2" descr="画面の領域">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000003000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -8401,7 +8453,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="27" name="図 26" descr="画面の領域"/>
+        <xdr:cNvPr id="27" name="図 26" descr="画面の領域">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00001B000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -8445,7 +8503,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="7" name="図 6" descr="画面の領域"/>
+        <xdr:cNvPr id="7" name="図 6" descr="画面の領域">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000007000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -8489,7 +8553,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="8" name="図 7" descr="画面の領域"/>
+        <xdr:cNvPr id="8" name="図 7" descr="画面の領域">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000008000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -8533,7 +8603,13 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="31" name="図 30" descr="画面の領域"/>
+        <xdr:cNvPr id="31" name="図 30" descr="画面の領域">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00001F000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvPicPr>
           <a:picLocks noChangeAspect="1"/>
         </xdr:cNvPicPr>
@@ -8577,20 +8653,32 @@
     </xdr:to>
     <xdr:grpSp>
       <xdr:nvGrpSpPr>
-        <xdr:cNvPr id="40" name="グループ化 39"/>
+        <xdr:cNvPr id="40" name="グループ化 39">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000028000000}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
         <xdr:cNvGrpSpPr/>
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="29718000" y="9666514"/>
-          <a:ext cx="13839119" cy="7508108"/>
+          <a:off x="30007601" y="9501380"/>
+          <a:ext cx="13983714" cy="7369470"/>
           <a:chOff x="29718000" y="9666514"/>
           <a:chExt cx="13839119" cy="7508108"/>
         </a:xfrm>
       </xdr:grpSpPr>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="41" name="図 40" descr="画面の領域"/>
+          <xdr:cNvPr id="41" name="図 40" descr="画面の領域">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-000029000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvPicPr>
             <a:picLocks noChangeAspect="1"/>
           </xdr:cNvPicPr>
@@ -8619,7 +8707,13 @@
       </xdr:pic>
       <xdr:pic>
         <xdr:nvPicPr>
-          <xdr:cNvPr id="42" name="図 41" descr="画面の領域"/>
+          <xdr:cNvPr id="42" name="図 41" descr="画面の領域">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0600-00002A000000}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
           <xdr:cNvPicPr>
             <a:picLocks noChangeAspect="1"/>
           </xdr:cNvPicPr>
@@ -8649,13 +8743,289 @@
     </xdr:grpSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>24646</xdr:colOff>
+      <xdr:row>59</xdr:row>
+      <xdr:rowOff>147882</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>29</xdr:col>
+      <xdr:colOff>443645</xdr:colOff>
+      <xdr:row>65</xdr:row>
+      <xdr:rowOff>147882</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="正方形/長方形 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{70F65659-BFFE-4F40-9C3E-5C02156A6024}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="19557315" y="12372745"/>
+          <a:ext cx="1651343" cy="961228"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>406675</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>123235</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>601675</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>8699</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="4" name="線吹き出し 1 (枠付き) 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9B49CEF-897A-4D03-8C25-9F4CC2FE8C9D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="13568119" y="11226664"/>
+          <a:ext cx="2253017" cy="1167102"/>
+        </a:xfrm>
+        <a:prstGeom prst="borderCallout1">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val 52087"/>
+            <a:gd name="adj2" fmla="val 100142"/>
+            <a:gd name="adj3" fmla="val 122156"/>
+            <a:gd name="adj4" fmla="val 265388"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent5">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="50000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>仕様の表記が誤っているが</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>BA</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>表より以下となる。</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>〇「</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>DDM1S17</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>」</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>✖「</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>VSC1S95</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1200" b="1">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            </a:rPr>
+            <a:t>」</a:t>
+          </a:r>
+          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1200" b="1">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+            <a:cs typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+          </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office テーマ">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -8693,9 +9063,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -8730,7 +9100,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -8765,7 +9135,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -8938,16 +9308,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B2:R13"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="1" max="1" width="4.44140625" customWidth="1"/>
+    <col min="1" max="1" width="4.5" customWidth="1"/>
     <col min="2" max="2" width="9" style="10" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="69.44140625" customWidth="1"/>
-    <col min="5" max="6" width="12.77734375" customWidth="1"/>
-    <col min="7" max="18" width="13.109375" customWidth="1"/>
+    <col min="4" max="4" width="69.5" customWidth="1"/>
+    <col min="5" max="6" width="12.75" customWidth="1"/>
+    <col min="7" max="18" width="13.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:18" ht="25.5" customHeight="1">
@@ -9017,7 +9387,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="2:18" ht="13.8" thickBot="1"/>
+    <row r="6" spans="2:18" ht="13.6" thickBot="1"/>
     <row r="7" spans="2:18">
       <c r="C7" s="248" t="s">
         <v>0</v>
@@ -9044,7 +9414,7 @@
       <c r="Q7" s="252"/>
       <c r="R7" s="253"/>
     </row>
-    <row r="8" spans="2:18" ht="27" thickBot="1">
+    <row r="8" spans="2:18" ht="26.5" thickBot="1">
       <c r="B8" s="10" t="s">
         <v>91</v>
       </c>
@@ -9097,7 +9467,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:18" ht="106.2" thickTop="1">
+    <row r="9" spans="2:18" ht="103.95" thickTop="1">
       <c r="B9" s="10">
         <f>IF(C9=0,0,ROW()-ROW($B$8))</f>
         <v>1</v>
@@ -9106,7 +9476,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="247" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="E9" s="14" t="s">
         <v>30</v>
@@ -9137,7 +9507,7 @@
       <c r="O9" s="14"/>
       <c r="P9" s="238"/>
       <c r="Q9" s="14" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="R9" s="182">
         <v>44279</v>
@@ -9209,7 +9579,7 @@
       <c r="Q12" s="1"/>
       <c r="R12" s="3"/>
     </row>
-    <row r="13" spans="2:18" ht="13.8" thickBot="1">
+    <row r="13" spans="2:18" ht="13.6" thickBot="1">
       <c r="B13" s="10">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -9242,22 +9612,25 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <hyperlinks>
-    <hyperlink ref="I3" r:id="rId1"/>
+    <hyperlink ref="I3" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:E39"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="4.6640625" customWidth="1"/>
-    <col min="3" max="3" width="3.44140625" customWidth="1"/>
-    <col min="4" max="4" width="17.44140625" customWidth="1"/>
+    <col min="2" max="2" width="4.625" customWidth="1"/>
+    <col min="3" max="3" width="3.5" customWidth="1"/>
+    <col min="4" max="4" width="17.5" customWidth="1"/>
     <col min="5" max="5" width="106" customWidth="1"/>
   </cols>
   <sheetData>
@@ -9271,13 +9644,13 @@
         <v>137</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="13.8" thickBot="1">
+    <row r="6" spans="2:5" ht="13.6" thickBot="1">
       <c r="B6" s="145" t="s">
         <v>128</v>
       </c>
       <c r="C6" s="145"/>
     </row>
-    <row r="7" spans="2:5" ht="13.8" thickBot="1">
+    <row r="7" spans="2:5" ht="13.6" thickBot="1">
       <c r="C7" s="74" t="s">
         <v>130</v>
       </c>
@@ -9297,7 +9670,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="26.4">
+    <row r="9" spans="2:5" ht="25.85">
       <c r="C9" s="155">
         <v>1</v>
       </c>
@@ -9308,7 +9681,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="13.8" thickBot="1">
+    <row r="10" spans="2:5" ht="13.6" thickBot="1">
       <c r="C10" s="153"/>
       <c r="D10" s="85"/>
       <c r="E10" s="6"/>
@@ -9316,14 +9689,14 @@
     <row r="11" spans="2:5">
       <c r="C11" s="151"/>
     </row>
-    <row r="12" spans="2:5" ht="13.8" thickBot="1">
+    <row r="12" spans="2:5" ht="13.6" thickBot="1">
       <c r="B12" s="146" t="s">
         <v>129</v>
       </c>
       <c r="C12" s="81"/>
       <c r="D12" s="81"/>
     </row>
-    <row r="13" spans="2:5" ht="13.8" thickBot="1">
+    <row r="13" spans="2:5" ht="13.6" thickBot="1">
       <c r="B13" s="147"/>
       <c r="C13" s="152" t="s">
         <v>130</v>
@@ -9335,7 +9708,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="13.8" thickTop="1">
+    <row r="14" spans="2:5" ht="13.6" thickTop="1">
       <c r="C14" s="149">
         <v>0</v>
       </c>
@@ -9412,17 +9785,17 @@
         <v>165</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="13.8" thickBot="1">
+    <row r="21" spans="2:5" ht="13.6" thickBot="1">
       <c r="C21" s="153"/>
       <c r="D21" s="85"/>
       <c r="E21" s="6"/>
     </row>
-    <row r="24" spans="2:5" ht="13.8" thickBot="1">
+    <row r="24" spans="2:5" ht="13.6" thickBot="1">
       <c r="B24" s="145" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="13.8" thickBot="1">
+    <row r="25" spans="2:5" ht="13.6" thickBot="1">
       <c r="C25" s="152" t="s">
         <v>130</v>
       </c>
@@ -9444,7 +9817,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="27" spans="2:5" ht="120" customHeight="1">
+    <row r="27" spans="2:5" ht="120.1" customHeight="1">
       <c r="C27" s="150">
         <v>1</v>
       </c>
@@ -9509,12 +9882,12 @@
       <c r="D33" s="84"/>
       <c r="E33" s="70"/>
     </row>
-    <row r="34" spans="2:5" ht="13.8" thickBot="1">
+    <row r="34" spans="2:5" ht="13.6" thickBot="1">
       <c r="C34" s="153"/>
       <c r="D34" s="85"/>
       <c r="E34" s="6"/>
     </row>
-    <row r="37" spans="2:5" ht="13.8" thickBot="1">
+    <row r="37" spans="2:5" ht="13.6" thickBot="1">
       <c r="B37" s="145" t="s">
         <v>161</v>
       </c>
@@ -9526,7 +9899,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="13.8" thickBot="1">
+    <row r="39" spans="2:5" ht="13.6" thickBot="1">
       <c r="C39" s="259"/>
       <c r="D39" s="260"/>
       <c r="E39" s="6" t="s">
@@ -9540,145 +9913,148 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <hyperlinks>
-    <hyperlink ref="E8" r:id="rId1"/>
-    <hyperlink ref="E9" r:id="rId2"/>
+    <hyperlink ref="E8" r:id="rId1" xr:uid="{00000000-0004-0000-0100-000000000000}"/>
+    <hyperlink ref="E9" r:id="rId2" xr:uid="{00000000-0004-0000-0100-000001000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet2">
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:N37"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="3.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="26.77734375" customWidth="1"/>
-    <col min="9" max="9" width="20.88671875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="26.75" customWidth="1"/>
+    <col min="9" max="9" width="20.875" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="13.8" thickBot="1"/>
+    <row r="1" spans="2:14" ht="13.6" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="261" t="s">
+      <c r="B2" s="286" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="262"/>
-      <c r="D2" s="267" t="s">
-        <v>296</v>
-      </c>
-      <c r="E2" s="268"/>
-      <c r="F2" s="268"/>
-      <c r="G2" s="268"/>
-      <c r="H2" s="269"/>
+      <c r="C2" s="287"/>
+      <c r="D2" s="274" t="s">
+        <v>293</v>
+      </c>
+      <c r="E2" s="275"/>
+      <c r="F2" s="275"/>
+      <c r="G2" s="275"/>
+      <c r="H2" s="276"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="263" t="s">
+      <c r="B3" s="261" t="s">
         <v>115</v>
       </c>
-      <c r="C3" s="264"/>
-      <c r="D3" s="270" t="s">
-        <v>294</v>
-      </c>
-      <c r="E3" s="271"/>
-      <c r="F3" s="271"/>
-      <c r="G3" s="271"/>
-      <c r="H3" s="272"/>
-    </row>
-    <row r="4" spans="2:14" ht="13.8" thickBot="1">
-      <c r="B4" s="265" t="s">
+      <c r="C3" s="262"/>
+      <c r="D3" s="277" t="s">
+        <v>291</v>
+      </c>
+      <c r="E3" s="278"/>
+      <c r="F3" s="278"/>
+      <c r="G3" s="278"/>
+      <c r="H3" s="279"/>
+    </row>
+    <row r="4" spans="2:14" ht="13.6" thickBot="1">
+      <c r="B4" s="272" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="266"/>
-      <c r="D4" s="273" t="str">
+      <c r="C4" s="273"/>
+      <c r="D4" s="280" t="str">
         <f ca="1">表紙!D3&amp;".c"</f>
         <v>alert_C_MCBW-CSTD-0-01-B-C0.c</v>
       </c>
-      <c r="E4" s="274"/>
-      <c r="F4" s="274"/>
-      <c r="G4" s="274"/>
-      <c r="H4" s="275"/>
-    </row>
-    <row r="5" spans="2:14" ht="13.8" thickBot="1">
+      <c r="E4" s="281"/>
+      <c r="F4" s="281"/>
+      <c r="G4" s="281"/>
+      <c r="H4" s="282"/>
+    </row>
+    <row r="5" spans="2:14" ht="13.6" thickBot="1">
       <c r="D5" t="str">
         <f ca="1">IF(LEN(表紙!D3&amp;".c") = LENB(表紙!D3&amp;".c"),"※モジュール名 全角チェックOK","※モジュール名 全角チェックNG：ファイル名に全角文字が使用されています！")</f>
         <v>※モジュール名 全角チェックOK</v>
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="261" t="s">
+      <c r="B6" s="286" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="262"/>
-      <c r="D6" s="276" t="str">
+      <c r="C6" s="287"/>
+      <c r="D6" s="283" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>C_MCBW</v>
       </c>
-      <c r="E6" s="277"/>
-      <c r="F6" s="277"/>
-      <c r="G6" s="277"/>
-      <c r="H6" s="278"/>
+      <c r="E6" s="284"/>
+      <c r="F6" s="284"/>
+      <c r="G6" s="284"/>
+      <c r="H6" s="285"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="263" t="s">
+      <c r="B7" s="261" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="264"/>
-      <c r="D7" s="279">
+      <c r="C7" s="262"/>
+      <c r="D7" s="263">
         <f>COUNTA($D$13:$D$37)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="280"/>
-      <c r="F7" s="280"/>
-      <c r="G7" s="280"/>
-      <c r="H7" s="281"/>
+      <c r="E7" s="264"/>
+      <c r="F7" s="264"/>
+      <c r="G7" s="264"/>
+      <c r="H7" s="265"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="263" t="s">
+      <c r="B8" s="261" t="s">
         <v>94</v>
       </c>
-      <c r="C8" s="264"/>
-      <c r="D8" s="279" t="str">
+      <c r="C8" s="262"/>
+      <c r="D8" s="263" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_C_MCBW_MTRX</v>
       </c>
-      <c r="E8" s="280"/>
-      <c r="F8" s="280"/>
-      <c r="G8" s="280"/>
-      <c r="H8" s="281"/>
+      <c r="E8" s="264"/>
+      <c r="F8" s="264"/>
+      <c r="G8" s="264"/>
+      <c r="H8" s="265"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="263" t="s">
+      <c r="B9" s="261" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="264"/>
-      <c r="D9" s="282" t="s">
-        <v>278</v>
-      </c>
-      <c r="E9" s="283"/>
-      <c r="F9" s="283"/>
-      <c r="G9" s="283"/>
-      <c r="H9" s="284"/>
-    </row>
-    <row r="10" spans="2:14" ht="13.8" thickBot="1">
-      <c r="B10" s="265" t="s">
+      <c r="C9" s="262"/>
+      <c r="D9" s="266" t="s">
+        <v>275</v>
+      </c>
+      <c r="E9" s="267"/>
+      <c r="F9" s="267"/>
+      <c r="G9" s="267"/>
+      <c r="H9" s="268"/>
+    </row>
+    <row r="10" spans="2:14" ht="13.6" thickBot="1">
+      <c r="B10" s="272" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="266"/>
-      <c r="D10" s="285"/>
-      <c r="E10" s="286"/>
-      <c r="F10" s="286"/>
-      <c r="G10" s="286"/>
-      <c r="H10" s="287"/>
-    </row>
-    <row r="11" spans="2:14" ht="13.8" thickBot="1"/>
-    <row r="12" spans="2:14" ht="13.8" thickBot="1">
+      <c r="C10" s="273"/>
+      <c r="D10" s="269"/>
+      <c r="E10" s="270"/>
+      <c r="F10" s="270"/>
+      <c r="G10" s="270"/>
+      <c r="H10" s="271"/>
+    </row>
+    <row r="11" spans="2:14" ht="13.6" thickBot="1"/>
+    <row r="12" spans="2:14" ht="13.6" thickBot="1">
       <c r="B12" s="136" t="s">
         <v>33</v>
       </c>
@@ -9713,7 +10089,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="13.8" thickTop="1">
+    <row r="13" spans="2:14" ht="13.6" thickTop="1">
       <c r="B13" s="103">
         <v>1</v>
       </c>
@@ -10566,7 +10942,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="13.8" thickBot="1">
+    <row r="37" spans="2:14" ht="13.6" thickBot="1">
       <c r="B37" s="94">
         <v>25</v>
       </c>
@@ -10607,76 +10983,79 @@
     <protectedRange sqref="D2:H3 D9:H10 C13:E37" name="編集許可"/>
   </protectedRanges>
   <mergeCells count="16">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="D2:H2"/>
+    <mergeCell ref="D3:H3"/>
+    <mergeCell ref="D4:H4"/>
+    <mergeCell ref="D6:H6"/>
+    <mergeCell ref="D7:H7"/>
     <mergeCell ref="B9:C9"/>
     <mergeCell ref="D8:H8"/>
     <mergeCell ref="D9:H9"/>
     <mergeCell ref="D10:H10"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="B8:C8"/>
-    <mergeCell ref="D2:H2"/>
-    <mergeCell ref="D3:H3"/>
-    <mergeCell ref="D4:H4"/>
-    <mergeCell ref="D6:H6"/>
-    <mergeCell ref="D7:H7"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B6:C6"/>
-    <mergeCell ref="B7:C7"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
   <conditionalFormatting sqref="C13:C37">
-    <cfRule type="expression" dxfId="17" priority="4">
+    <cfRule type="expression" dxfId="6" priority="4">
       <formula>14&lt;LEN($D$6)+LEN($C13)</formula>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="D5">
+    <cfRule type="containsText" dxfId="5" priority="1" operator="containsText" text="NG">
+      <formula>NOT(ISERROR(SEARCH("NG",D5)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="D6">
-    <cfRule type="expression" dxfId="16" priority="3">
+    <cfRule type="expression" dxfId="4" priority="3">
       <formula>14 &lt; LEN($D$6)</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="D5">
-    <cfRule type="containsText" dxfId="15" priority="1" operator="containsText" text="NG">
-      <formula>NOT(ISERROR(SEARCH("NG",D5)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E13:E37">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E13:E37" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"○,－"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D13:D37">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D13:D37" xr:uid="{00000000-0002-0000-0200-000001000000}">
       <formula1>$K$13:$K$37</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D9">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D9" xr:uid="{00000000-0002-0000-0200-000002000000}">
       <formula1>$L$13:$L$14</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr codeName="Sheet7">
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B2:R59"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="3.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="36.44140625" customWidth="1"/>
-    <col min="6" max="6" width="52.77734375" customWidth="1"/>
-    <col min="7" max="7" width="7.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="3.88671875" customWidth="1"/>
-    <col min="16" max="16" width="9.88671875" customWidth="1"/>
-    <col min="17" max="17" width="44.6640625" customWidth="1"/>
-    <col min="18" max="18" width="73.6640625" customWidth="1"/>
+    <col min="5" max="5" width="36.5" customWidth="1"/>
+    <col min="6" max="6" width="52.75" customWidth="1"/>
+    <col min="7" max="7" width="7.125" bestFit="1" customWidth="1"/>
+    <col min="8" max="15" width="3.875" customWidth="1"/>
+    <col min="16" max="16" width="9.875" customWidth="1"/>
+    <col min="17" max="17" width="44.625" customWidth="1"/>
+    <col min="18" max="18" width="73.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="13.8" thickBot="1">
+    <row r="2" spans="2:18" ht="13.6" thickBot="1">
       <c r="B2" t="s">
         <v>186</v>
       </c>
@@ -10684,7 +11063,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="13.8" thickBot="1">
+    <row r="3" spans="2:18" ht="13.6" thickBot="1">
       <c r="B3" s="136" t="s">
         <v>33</v>
       </c>
@@ -10722,7 +11101,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="13.8" hidden="1" thickTop="1">
+    <row r="4" spans="2:18" ht="13.6" hidden="1" thickTop="1">
       <c r="B4" s="167">
         <v>0</v>
       </c>
@@ -10750,7 +11129,7 @@
       </c>
       <c r="R4" s="135"/>
     </row>
-    <row r="5" spans="2:18" ht="13.8" thickTop="1">
+    <row r="5" spans="2:18" ht="13.6" thickTop="1">
       <c r="B5" s="170">
         <v>1</v>
       </c>
@@ -11278,7 +11657,7 @@
       <c r="Q28" s="140"/>
       <c r="R28" s="113"/>
     </row>
-    <row r="29" spans="2:18" ht="13.8" thickBot="1">
+    <row r="29" spans="2:18" ht="13.6" thickBot="1">
       <c r="B29" s="171">
         <v>25</v>
       </c>
@@ -11300,7 +11679,7 @@
       <c r="Q29" s="138"/>
       <c r="R29" s="115"/>
     </row>
-    <row r="32" spans="2:18" ht="13.8" thickBot="1">
+    <row r="32" spans="2:18" ht="13.6" thickBot="1">
       <c r="B32" t="s">
         <v>187</v>
       </c>
@@ -11308,7 +11687,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="13.8" thickBot="1">
+    <row r="33" spans="2:18" ht="13.6" thickBot="1">
       <c r="B33" s="136" t="s">
         <v>33</v>
       </c>
@@ -11340,7 +11719,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="34" spans="2:18" ht="13.8" hidden="1" thickTop="1">
+    <row r="34" spans="2:18" ht="13.6" hidden="1" thickTop="1">
       <c r="B34" s="167">
         <v>0</v>
       </c>
@@ -11366,7 +11745,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="35" spans="2:18" ht="13.8" thickTop="1">
+    <row r="35" spans="2:18" ht="13.6" thickTop="1">
       <c r="B35" s="170">
         <v>1</v>
       </c>
@@ -11894,7 +12273,7 @@
       <c r="Q58" s="140"/>
       <c r="R58" s="172"/>
     </row>
-    <row r="59" spans="2:18" ht="13.8" thickBot="1">
+    <row r="59" spans="2:18" ht="13.6" thickBot="1">
       <c r="B59" s="171">
         <v>25</v>
       </c>
@@ -11923,48 +12302,51 @@
   </protectedRanges>
   <phoneticPr fontId="2"/>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D29">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D5:D29" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"OPT,HW"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D35:D59">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D35:D59" xr:uid="{00000000-0002-0000-0300-000001000000}">
       <formula1>"DEF"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr codeName="Sheet3">
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:U103"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="28.33203125" customWidth="1"/>
-    <col min="3" max="3" width="15.88671875" customWidth="1"/>
-    <col min="5" max="5" width="12.33203125" customWidth="1"/>
-    <col min="6" max="6" width="19.77734375" customWidth="1"/>
-    <col min="7" max="7" width="12.33203125" customWidth="1"/>
+    <col min="2" max="2" width="28.375" customWidth="1"/>
+    <col min="3" max="3" width="15.875" customWidth="1"/>
+    <col min="5" max="5" width="12.375" customWidth="1"/>
+    <col min="6" max="6" width="19.75" customWidth="1"/>
+    <col min="7" max="7" width="12.375" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="12.33203125" customWidth="1"/>
-    <col min="10" max="10" width="33.44140625" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" customWidth="1"/>
-    <col min="12" max="12" width="16.109375" customWidth="1"/>
-    <col min="14" max="14" width="30.109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="57.109375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="12.375" customWidth="1"/>
+    <col min="10" max="10" width="33.5" customWidth="1"/>
+    <col min="11" max="11" width="12.375" customWidth="1"/>
+    <col min="12" max="12" width="16.125" customWidth="1"/>
+    <col min="14" max="14" width="30.125" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="57.125" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="13.8" thickBot="1">
+    <row r="1" spans="2:21" ht="13.6" thickBot="1">
       <c r="C1" s="87" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="13.8" thickBot="1">
+    <row r="2" spans="2:21" ht="13.6" thickBot="1">
       <c r="B2" s="95" t="s">
         <v>57</v>
       </c>
@@ -12008,7 +12390,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="14.4" hidden="1" thickTop="1" thickBot="1">
+    <row r="3" spans="2:21" ht="14.3" hidden="1" thickTop="1" thickBot="1">
       <c r="B3" s="25"/>
       <c r="C3" s="46" t="s">
         <v>107</v>
@@ -12029,9 +12411,9 @@
         <v>97</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="13.8" thickTop="1">
+    <row r="4" spans="2:21" ht="13.6" thickTop="1">
       <c r="B4" s="207" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C4" s="197" t="s">
         <v>207</v>
@@ -12043,19 +12425,19 @@
         <v>125</v>
       </c>
       <c r="F4" s="231" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G4" s="230" t="s">
         <v>125</v>
       </c>
       <c r="H4" s="231" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="I4" s="230" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="J4" s="231" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="K4" s="230" t="s">
         <v>125</v>
@@ -12081,7 +12463,7 @@
     </row>
     <row r="5" spans="2:21">
       <c r="B5" s="207" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C5" s="105" t="s">
         <v>200</v>
@@ -12093,7 +12475,7 @@
         <v>125</v>
       </c>
       <c r="F5" s="199" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="G5" s="207" t="s">
         <v>125</v>
@@ -12102,16 +12484,16 @@
         <v>214</v>
       </c>
       <c r="I5" s="207" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="J5" s="231" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="K5" s="207" t="s">
         <v>125</v>
       </c>
       <c r="L5" s="199" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="M5" s="42">
         <f t="shared" ref="M5:M68" ca="1" si="1">LEN(N5)</f>
@@ -12319,7 +12701,7 @@
       </c>
       <c r="U12" s="31"/>
     </row>
-    <row r="13" spans="2:21" ht="13.8" thickBot="1">
+    <row r="13" spans="2:21" ht="13.6" thickBot="1">
       <c r="B13" s="25"/>
       <c r="C13" s="24"/>
       <c r="D13" s="112"/>
@@ -14570,7 +14952,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="2:15" ht="13.8" thickBot="1">
+    <row r="103" spans="2:15" ht="13.6" thickBot="1">
       <c r="B103" s="48"/>
       <c r="C103" s="49"/>
       <c r="D103" s="114"/>
@@ -14601,33 +14983,31 @@
     <protectedRange sqref="B4:L103" name="範囲1"/>
   </protectedRanges>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="M4:M103">
-    <cfRule type="cellIs" dxfId="14" priority="2" operator="greaterThan">
-      <formula>32</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="M3">
-    <cfRule type="cellIs" dxfId="13" priority="1" operator="greaterThan">
+  <conditionalFormatting sqref="M3:M103">
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="greaterThan">
       <formula>32</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3 G3 I3 E3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="K3 G3 I3 E3" xr:uid="{00000000-0002-0000-0400-000000000000}">
       <formula1>"あり,なし"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <legacyDrawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0400-000001000000}">
           <x14:formula1>
             <xm:f>Matrix!$H$13:$H$37</xm:f>
           </x14:formula1>
           <xm:sqref>B3:B103</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0400-000002000000}">
           <x14:formula1>
             <xm:f>Config_IF!$C$4:$C$29</xm:f>
           </x14:formula1>
@@ -14640,23 +15020,23 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <sheetPr codeName="Sheet8">
     <tabColor rgb="FFCCECFF"/>
   </sheetPr>
   <dimension ref="A1:AW199"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="16.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
     <col min="4" max="35" width="3" customWidth="1"/>
-    <col min="36" max="36" width="36.33203125" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.109375" customWidth="1"/>
+    <col min="36" max="36" width="36.375" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.125" customWidth="1"/>
     <col min="38" max="42" width="9" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="20.6640625" hidden="1" customWidth="1"/>
-    <col min="44" max="47" width="41.109375" customWidth="1"/>
-    <col min="48" max="48" width="23.6640625" customWidth="1"/>
+    <col min="43" max="43" width="20.625" hidden="1" customWidth="1"/>
+    <col min="44" max="47" width="41.125" customWidth="1"/>
+    <col min="48" max="48" width="23.625" customWidth="1"/>
     <col min="49" max="49" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -14775,7 +15155,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="3" spans="1:49" ht="213" customHeight="1" thickBot="1">
+    <row r="3" spans="1:49" ht="212.95" customHeight="1" thickBot="1">
       <c r="B3" s="239" t="str">
         <f>IF(OR(IF(COUNTIF(D6:AC69,"0")&lt;&gt;0,TRUE,FALSE),IF(COUNTIF(D6:AC69,"1")&lt;&gt;0,TRUE,FALSE)),"Search Table","Index Table")</f>
         <v>Index Table</v>
@@ -14863,14 +15243,14 @@
         <v>65</v>
       </c>
       <c r="AE3" s="189" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="AF3" s="296" t="s">
-        <v>251</v>
+        <v>295</v>
       </c>
       <c r="AG3" s="297"/>
       <c r="AH3" s="296" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="AI3" s="297"/>
       <c r="AJ3" s="291"/>
@@ -14878,7 +15258,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="13.8" thickBot="1">
+    <row r="4" spans="1:49" ht="13.6" thickBot="1">
       <c r="A4" s="292" t="s">
         <v>62</v>
       </c>
@@ -14926,7 +15306,7 @@
       <c r="AV4" s="77"/>
       <c r="AW4" s="78"/>
     </row>
-    <row r="5" spans="1:49" ht="13.8" thickBot="1">
+    <row r="5" spans="1:49" ht="13.6" thickBot="1">
       <c r="A5" s="294"/>
       <c r="B5" s="295"/>
       <c r="C5" s="134"/>
@@ -16443,7 +16823,7 @@
         <v>ALERT_VOM_IGN_ON</v>
       </c>
     </row>
-    <row r="17" spans="2:49" ht="13.8" thickBot="1">
+    <row r="17" spans="2:49" ht="13.6" thickBot="1">
       <c r="B17" s="130"/>
       <c r="C17" s="42">
         <f t="shared" si="2"/>
@@ -22855,7 +23235,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="13.8" thickBot="1">
+    <row r="70" spans="1:46" ht="13.6" thickBot="1">
       <c r="A70" s="51" t="s">
         <v>63</v>
       </c>
@@ -43449,65 +43829,28 @@
     <mergeCell ref="AF3:AG3"/>
   </mergeCells>
   <phoneticPr fontId="2"/>
-  <conditionalFormatting sqref="D6:AB11 D12:AC69">
-    <cfRule type="cellIs" dxfId="12" priority="54" operator="equal">
+  <conditionalFormatting sqref="D6:AI69">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="equal">
       <formula>1</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="11" priority="55" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="equal">
       <formula>"×"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="AR5:AS70">
-    <cfRule type="expression" dxfId="10" priority="53">
+    <cfRule type="expression" dxfId="0" priority="53">
       <formula>$B$3="Index Table"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="AC6:AC11">
-    <cfRule type="cellIs" dxfId="9" priority="51" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="8" priority="52" operator="equal">
-      <formula>"×"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE6:AI37">
-    <cfRule type="cellIs" dxfId="7" priority="7" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="8" operator="equal">
-      <formula>"×"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AD6:AD69">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
-      <formula>"×"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE38:AI38">
-    <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="4" operator="equal">
-      <formula>"×"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="AE39:AI69">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="equal">
-      <formula>1</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="equal">
-      <formula>"×"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0500-000000000000}">
           <x14:formula1>
             <xm:f>CH_Design!$C$3:$C$103</xm:f>
           </x14:formula1>
@@ -43520,25 +43863,25 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B2:AT90"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="48.6640625" customWidth="1"/>
-    <col min="3" max="10" width="3.33203125" customWidth="1"/>
-    <col min="11" max="11" width="20.88671875" customWidth="1"/>
+    <col min="2" max="2" width="48.625" customWidth="1"/>
+    <col min="3" max="10" width="3.375" customWidth="1"/>
+    <col min="11" max="11" width="20.875" customWidth="1"/>
     <col min="12" max="12" width="19" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.88671875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="21" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.109375" customWidth="1"/>
-    <col min="17" max="17" width="8.21875" customWidth="1"/>
-    <col min="18" max="18" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.125" customWidth="1"/>
+    <col min="17" max="17" width="8.25" customWidth="1"/>
+    <col min="18" max="18" width="11.875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:46" ht="15" thickBot="1">
+    <row r="2" spans="2:46" ht="15.65" thickBot="1">
       <c r="B2" s="26" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="V2" s="188" t="s">
         <v>201</v>
@@ -43568,7 +43911,7 @@
       <c r="AS2" s="188"/>
       <c r="AT2" s="188"/>
     </row>
-    <row r="3" spans="2:46" ht="15" thickBot="1">
+    <row r="3" spans="2:46" ht="15.65" thickBot="1">
       <c r="B3" s="92" t="s">
         <v>122</v>
       </c>
@@ -43636,7 +43979,7 @@
       <c r="L5" s="220"/>
       <c r="M5" s="69"/>
       <c r="N5" s="31" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="O5" s="72" t="s">
         <v>23</v>
@@ -43651,7 +43994,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="2:46" ht="26.4">
+    <row r="6" spans="2:46" ht="25.85">
       <c r="B6" s="66" t="s">
         <v>32</v>
       </c>
@@ -43698,7 +44041,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="7" spans="2:46" ht="26.4">
+    <row r="7" spans="2:46" ht="25.85">
       <c r="B7" s="67" t="s">
         <v>27</v>
       </c>
@@ -43713,154 +44056,154 @@
       <c r="I7" s="299"/>
       <c r="J7" s="300"/>
       <c r="K7" s="28" t="s">
-        <v>218</v>
+        <v>296</v>
       </c>
       <c r="L7" s="1" t="s">
-        <v>218</v>
+        <v>296</v>
       </c>
       <c r="M7" s="28" t="s">
-        <v>218</v>
+        <v>296</v>
       </c>
       <c r="N7" s="32"/>
       <c r="O7" s="221"/>
       <c r="P7" s="222"/>
       <c r="Q7" s="73"/>
       <c r="R7" s="70" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="8" spans="2:46" ht="133.19999999999999">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="8" spans="2:46" ht="130.44999999999999">
       <c r="B8" s="66" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="159" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="D8" s="159" t="s">
         <v>61</v>
       </c>
       <c r="E8" s="159" t="s">
+        <v>219</v>
+      </c>
+      <c r="F8" s="159" t="s">
         <v>220</v>
       </c>
-      <c r="F8" s="159" t="s">
+      <c r="G8" s="159" t="s">
         <v>221</v>
       </c>
-      <c r="G8" s="159" t="s">
+      <c r="H8" s="159" t="s">
         <v>222</v>
       </c>
-      <c r="H8" s="159" t="s">
+      <c r="I8" s="159" t="s">
         <v>223</v>
       </c>
-      <c r="I8" s="159" t="s">
+      <c r="J8" s="159" t="s">
         <v>224</v>
       </c>
-      <c r="J8" s="159" t="s">
+      <c r="K8" s="28" t="s">
+        <v>281</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>295</v>
+      </c>
+      <c r="M8" s="28" t="s">
+        <v>280</v>
+      </c>
+      <c r="N8" s="31" t="s">
         <v>225</v>
-      </c>
-      <c r="K8" s="28" t="s">
-        <v>284</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>226</v>
-      </c>
-      <c r="M8" s="28" t="s">
-        <v>283</v>
-      </c>
-      <c r="N8" s="31" t="s">
-        <v>227</v>
       </c>
       <c r="O8" s="221"/>
       <c r="P8" s="222"/>
       <c r="Q8" s="73"/>
       <c r="R8" s="185" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="9" spans="2:46" ht="79.8" thickBot="1">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="9" spans="2:46" ht="78.150000000000006" thickBot="1">
       <c r="B9" s="68" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="160" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="D9" s="160" t="s">
         <v>214</v>
       </c>
       <c r="E9" s="160" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="F9" s="160" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G9" s="160" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="H9" s="160" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="I9" s="160" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="J9" s="160" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="K9" s="29" t="s">
         <v>197</v>
       </c>
       <c r="L9" s="27" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="M9" s="29" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="N9" s="33" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="O9" s="223"/>
       <c r="P9" s="27" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="Q9" s="71"/>
       <c r="R9" s="186" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="10" spans="2:46" ht="13.8" thickTop="1">
+    <row r="10" spans="2:46" ht="13.6" thickTop="1">
       <c r="B10" s="224" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="C10" s="161" t="s">
+        <v>231</v>
+      </c>
+      <c r="D10" s="161" t="s">
+        <v>231</v>
+      </c>
+      <c r="E10" s="161" t="s">
+        <v>231</v>
+      </c>
+      <c r="F10" s="161" t="s">
+        <v>231</v>
+      </c>
+      <c r="G10" s="161" t="s">
+        <v>231</v>
+      </c>
+      <c r="H10" s="161" t="s">
+        <v>231</v>
+      </c>
+      <c r="I10" s="161" t="s">
+        <v>231</v>
+      </c>
+      <c r="J10" s="161" t="s">
+        <v>231</v>
+      </c>
+      <c r="K10" s="225" t="s">
+        <v>249</v>
+      </c>
+      <c r="L10" s="226" t="s">
+        <v>232</v>
+      </c>
+      <c r="M10" s="195" t="s">
         <v>233</v>
-      </c>
-      <c r="D10" s="161" t="s">
-        <v>233</v>
-      </c>
-      <c r="E10" s="161" t="s">
-        <v>233</v>
-      </c>
-      <c r="F10" s="161" t="s">
-        <v>233</v>
-      </c>
-      <c r="G10" s="161" t="s">
-        <v>233</v>
-      </c>
-      <c r="H10" s="161" t="s">
-        <v>233</v>
-      </c>
-      <c r="I10" s="161" t="s">
-        <v>233</v>
-      </c>
-      <c r="J10" s="161" t="s">
-        <v>233</v>
-      </c>
-      <c r="K10" s="225" t="s">
-        <v>252</v>
-      </c>
-      <c r="L10" s="226" t="s">
-        <v>234</v>
-      </c>
-      <c r="M10" s="195" t="s">
-        <v>235</v>
       </c>
       <c r="N10" s="196" t="s">
         <v>31</v>
@@ -43876,40 +44219,40 @@
     </row>
     <row r="11" spans="2:46">
       <c r="B11" s="194" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="C11" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D11" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E11" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F11" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G11" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H11" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I11" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J11" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K11" s="227" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="L11" s="217" t="s">
+        <v>234</v>
+      </c>
+      <c r="M11" s="228" t="s">
         <v>236</v>
-      </c>
-      <c r="M11" s="228" t="s">
-        <v>238</v>
       </c>
       <c r="N11" s="203" t="s">
         <v>31</v>
@@ -43925,40 +44268,40 @@
     </row>
     <row r="12" spans="2:46">
       <c r="B12" s="194" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="C12" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D12" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E12" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F12" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G12" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H12" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I12" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J12" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K12" s="227" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="L12" s="217" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="M12" s="228" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="N12" s="203" t="s">
         <v>31</v>
@@ -43974,47 +44317,47 @@
     </row>
     <row r="13" spans="2:46">
       <c r="B13" s="194" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="C13" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D13" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E13" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F13" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G13" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H13" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I13" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J13" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K13" s="227" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="L13" s="217" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="M13" s="228" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="N13" s="203" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="O13" s="162"/>
       <c r="P13" s="217" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="Q13" s="37"/>
       <c r="R13" s="211" t="s">
@@ -44023,40 +44366,40 @@
     </row>
     <row r="14" spans="2:46">
       <c r="B14" s="224" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="C14" s="162" t="s">
+        <v>231</v>
+      </c>
+      <c r="D14" s="162" t="s">
+        <v>231</v>
+      </c>
+      <c r="E14" s="162" t="s">
+        <v>231</v>
+      </c>
+      <c r="F14" s="162" t="s">
+        <v>231</v>
+      </c>
+      <c r="G14" s="162" t="s">
+        <v>231</v>
+      </c>
+      <c r="H14" s="162" t="s">
+        <v>231</v>
+      </c>
+      <c r="I14" s="162" t="s">
+        <v>231</v>
+      </c>
+      <c r="J14" s="162" t="s">
+        <v>231</v>
+      </c>
+      <c r="K14" s="227" t="s">
+        <v>241</v>
+      </c>
+      <c r="L14" s="217" t="s">
+        <v>234</v>
+      </c>
+      <c r="M14" s="195" t="s">
         <v>233</v>
-      </c>
-      <c r="D14" s="162" t="s">
-        <v>233</v>
-      </c>
-      <c r="E14" s="162" t="s">
-        <v>233</v>
-      </c>
-      <c r="F14" s="162" t="s">
-        <v>233</v>
-      </c>
-      <c r="G14" s="162" t="s">
-        <v>233</v>
-      </c>
-      <c r="H14" s="162" t="s">
-        <v>233</v>
-      </c>
-      <c r="I14" s="162" t="s">
-        <v>233</v>
-      </c>
-      <c r="J14" s="162" t="s">
-        <v>233</v>
-      </c>
-      <c r="K14" s="227" t="s">
-        <v>243</v>
-      </c>
-      <c r="L14" s="217" t="s">
-        <v>236</v>
-      </c>
-      <c r="M14" s="195" t="s">
-        <v>235</v>
       </c>
       <c r="N14" s="203" t="s">
         <v>31</v>
@@ -44072,40 +44415,40 @@
     </row>
     <row r="15" spans="2:46">
       <c r="B15" s="194" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="C15" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D15" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E15" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F15" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G15" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H15" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I15" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J15" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K15" s="229" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="L15" s="217" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="M15" s="228" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="N15" s="196" t="s">
         <v>31</v>
@@ -44121,40 +44464,40 @@
     </row>
     <row r="16" spans="2:46">
       <c r="B16" s="194" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="C16" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D16" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E16" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F16" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G16" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H16" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I16" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J16" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K16" s="229" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="L16" s="217" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="M16" s="228" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="N16" s="203" t="s">
         <v>31</v>
@@ -44170,47 +44513,47 @@
     </row>
     <row r="17" spans="2:46">
       <c r="B17" s="194" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="C17" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D17" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E17" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F17" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G17" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H17" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I17" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J17" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K17" s="229" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="L17" s="217" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="M17" s="228" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="N17" s="203" t="s">
         <v>200</v>
       </c>
       <c r="O17" s="201"/>
       <c r="P17" s="217" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="Q17" s="214"/>
       <c r="R17" s="211" t="s">
@@ -44219,40 +44562,40 @@
     </row>
     <row r="18" spans="2:46">
       <c r="B18" s="194" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C18" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D18" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E18" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F18" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G18" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H18" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I18" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J18" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K18" s="200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L18" s="195" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="M18" s="217" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="N18" s="203" t="s">
         <v>31</v>
@@ -44268,40 +44611,40 @@
     </row>
     <row r="19" spans="2:46">
       <c r="B19" s="194" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C19" s="162" t="s">
+        <v>231</v>
+      </c>
+      <c r="D19" s="162" t="s">
+        <v>231</v>
+      </c>
+      <c r="E19" s="162" t="s">
+        <v>231</v>
+      </c>
+      <c r="F19" s="162" t="s">
+        <v>231</v>
+      </c>
+      <c r="G19" s="162" t="s">
+        <v>231</v>
+      </c>
+      <c r="H19" s="162" t="s">
+        <v>231</v>
+      </c>
+      <c r="I19" s="162" t="s">
+        <v>231</v>
+      </c>
+      <c r="J19" s="162" t="s">
+        <v>231</v>
+      </c>
+      <c r="K19" s="200" t="s">
+        <v>259</v>
+      </c>
+      <c r="L19" s="195" t="s">
+        <v>260</v>
+      </c>
+      <c r="M19" s="195" t="s">
         <v>233</v>
-      </c>
-      <c r="D19" s="162" t="s">
-        <v>233</v>
-      </c>
-      <c r="E19" s="162" t="s">
-        <v>233</v>
-      </c>
-      <c r="F19" s="162" t="s">
-        <v>233</v>
-      </c>
-      <c r="G19" s="162" t="s">
-        <v>233</v>
-      </c>
-      <c r="H19" s="162" t="s">
-        <v>233</v>
-      </c>
-      <c r="I19" s="162" t="s">
-        <v>233</v>
-      </c>
-      <c r="J19" s="162" t="s">
-        <v>233</v>
-      </c>
-      <c r="K19" s="200" t="s">
-        <v>262</v>
-      </c>
-      <c r="L19" s="195" t="s">
-        <v>263</v>
-      </c>
-      <c r="M19" s="195" t="s">
-        <v>235</v>
       </c>
       <c r="N19" s="203" t="s">
         <v>31</v>
@@ -44317,40 +44660,40 @@
     </row>
     <row r="20" spans="2:46">
       <c r="B20" s="194" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C20" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D20" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E20" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F20" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G20" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H20" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I20" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J20" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K20" s="200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L20" s="195" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="M20" s="228" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="N20" s="203" t="s">
         <v>31</v>
@@ -44366,40 +44709,40 @@
     </row>
     <row r="21" spans="2:46">
       <c r="B21" s="194" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="C21" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D21" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E21" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F21" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G21" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H21" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I21" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J21" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K21" s="200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L21" s="195" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="M21" s="228" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="N21" s="203" t="s">
         <v>31</v>
@@ -44415,47 +44758,47 @@
     </row>
     <row r="22" spans="2:46">
       <c r="B22" s="194" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C22" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D22" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E22" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F22" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G22" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H22" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I22" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J22" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K22" s="200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L22" s="195" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="M22" s="228" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="N22" s="203" t="s">
         <v>200</v>
       </c>
       <c r="O22" s="162"/>
       <c r="P22" s="217" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="Q22" s="37"/>
       <c r="R22" s="211" t="s">
@@ -44464,40 +44807,40 @@
     </row>
     <row r="23" spans="2:46">
       <c r="B23" s="194" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C23" s="162" t="s">
+        <v>231</v>
+      </c>
+      <c r="D23" s="162" t="s">
+        <v>231</v>
+      </c>
+      <c r="E23" s="162" t="s">
+        <v>231</v>
+      </c>
+      <c r="F23" s="162" t="s">
+        <v>231</v>
+      </c>
+      <c r="G23" s="162" t="s">
+        <v>231</v>
+      </c>
+      <c r="H23" s="162" t="s">
+        <v>231</v>
+      </c>
+      <c r="I23" s="162" t="s">
+        <v>231</v>
+      </c>
+      <c r="J23" s="162" t="s">
+        <v>231</v>
+      </c>
+      <c r="K23" s="200" t="s">
+        <v>259</v>
+      </c>
+      <c r="L23" s="195" t="s">
+        <v>261</v>
+      </c>
+      <c r="M23" s="195" t="s">
         <v>233</v>
-      </c>
-      <c r="D23" s="162" t="s">
-        <v>233</v>
-      </c>
-      <c r="E23" s="162" t="s">
-        <v>233</v>
-      </c>
-      <c r="F23" s="162" t="s">
-        <v>233</v>
-      </c>
-      <c r="G23" s="162" t="s">
-        <v>233</v>
-      </c>
-      <c r="H23" s="162" t="s">
-        <v>233</v>
-      </c>
-      <c r="I23" s="162" t="s">
-        <v>233</v>
-      </c>
-      <c r="J23" s="162" t="s">
-        <v>233</v>
-      </c>
-      <c r="K23" s="200" t="s">
-        <v>262</v>
-      </c>
-      <c r="L23" s="195" t="s">
-        <v>264</v>
-      </c>
-      <c r="M23" s="195" t="s">
-        <v>235</v>
       </c>
       <c r="N23" s="203" t="s">
         <v>31</v>
@@ -44513,40 +44856,40 @@
     </row>
     <row r="24" spans="2:46">
       <c r="B24" s="194" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C24" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D24" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E24" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F24" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G24" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H24" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I24" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J24" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K24" s="200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L24" s="195" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="M24" s="228" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="N24" s="203" t="s">
         <v>31</v>
@@ -44562,40 +44905,40 @@
     </row>
     <row r="25" spans="2:46">
       <c r="B25" s="194" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="C25" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D25" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E25" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F25" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G25" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H25" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I25" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J25" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K25" s="200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L25" s="195" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="M25" s="228" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="N25" s="203" t="s">
         <v>31</v>
@@ -44611,40 +44954,40 @@
     </row>
     <row r="26" spans="2:46">
       <c r="B26" s="194" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="C26" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D26" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E26" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F26" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G26" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H26" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I26" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J26" s="162" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K26" s="200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="L26" s="195" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="M26" s="228" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="N26" s="246" t="s">
         <v>31</v>
@@ -44658,45 +45001,45 @@
         <v>211</v>
       </c>
     </row>
-    <row r="27" spans="2:46" ht="13.8" thickBot="1">
+    <row r="27" spans="2:46" ht="13.6" thickBot="1">
       <c r="B27" s="193" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="C27" s="201" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="D27" s="201" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E27" s="201" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="F27" s="201" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="G27" s="201" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="H27" s="201" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="I27" s="201" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="J27" s="201" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="K27" s="192" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="L27" s="213" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="M27" s="218" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="N27" s="232" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="O27" s="201"/>
       <c r="P27" s="218" t="s">
@@ -44707,7 +45050,7 @@
         <v>211</v>
       </c>
       <c r="V27" s="188" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="W27" s="188"/>
       <c r="X27" s="188"/>
@@ -45000,7 +45343,7 @@
       <c r="Q41" s="205"/>
       <c r="R41" s="205"/>
       <c r="V41" s="188" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="W41" s="188"/>
       <c r="X41" s="188"/>
@@ -45697,7 +46040,7 @@
     </row>
     <row r="90" spans="12:46">
       <c r="V90" s="188" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="W90" s="188"/>
       <c r="X90" s="188"/>
@@ -45732,28 +46075,31 @@
   </mergeCells>
   <phoneticPr fontId="2"/>
   <dataValidations disablePrompts="1" count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C3" xr:uid="{00000000-0002-0000-0600-000000000000}">
       <formula1>"Index,Matrix Search"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:D27"/>
-  <sheetFormatPr defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultRowHeight="12.9"/>
   <cols>
-    <col min="2" max="2" width="4.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.21875" customWidth="1"/>
+    <col min="2" max="2" width="4.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.25" customWidth="1"/>
     <col min="4" max="4" width="86" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="13.8" thickBot="1">
+    <row r="2" spans="2:4" ht="13.6" thickBot="1">
       <c r="B2" s="80" t="s">
         <v>84</v>
       </c>
@@ -45763,7 +46109,7 @@
       </c>
       <c r="D2" s="81"/>
     </row>
-    <row r="3" spans="2:4" ht="13.8" thickBot="1">
+    <row r="3" spans="2:4" ht="13.6" thickBot="1">
       <c r="B3" s="74" t="s">
         <v>84</v>
       </c>
@@ -45774,7 +46120,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="13.8" thickTop="1">
+    <row r="4" spans="2:4" ht="13.6" thickTop="1">
       <c r="B4" s="13">
         <v>0</v>
       </c>
@@ -45785,7 +46131,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="39.6">
+    <row r="5" spans="2:4" ht="38.75">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -45796,7 +46142,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="26.4">
+    <row r="6" spans="2:4" ht="25.85">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -45807,7 +46153,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="52.8">
+    <row r="7" spans="2:4" ht="51.65">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -45818,7 +46164,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="79.2">
+    <row r="8" spans="2:4" ht="77.45">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -45829,7 +46175,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="9" spans="2:4" ht="41.25" customHeight="1">
+    <row r="9" spans="2:4" ht="41.3" customHeight="1">
       <c r="B9" s="2">
         <v>5</v>
       </c>
@@ -45840,7 +46186,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="26.4">
+    <row r="10" spans="2:4" ht="25.85">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -45851,7 +46197,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="26.4">
+    <row r="11" spans="2:4" ht="25.85">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -45862,7 +46208,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="26.4">
+    <row r="12" spans="2:4" ht="25.85">
       <c r="B12" s="2">
         <v>8</v>
       </c>
@@ -45873,7 +46219,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="26.4">
+    <row r="13" spans="2:4" ht="25.85">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -45884,7 +46230,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="26.4">
+    <row r="14" spans="2:4" ht="25.85">
       <c r="B14" s="2">
         <v>10</v>
       </c>
@@ -45895,7 +46241,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="132">
+    <row r="15" spans="2:4" ht="129.1">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -45917,7 +46263,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="26.4">
+    <row r="17" spans="2:4" ht="25.85">
       <c r="B17" s="2">
         <v>13</v>
       </c>
@@ -45928,7 +46274,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="92.4">
+    <row r="18" spans="2:4" ht="90.35">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -45939,7 +46285,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="39.6">
+    <row r="19" spans="2:4" ht="38.75">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -45950,7 +46296,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="20" spans="2:4" ht="64.5" customHeight="1">
+    <row r="20" spans="2:4" ht="64.55" customHeight="1">
       <c r="B20" s="2">
         <v>16</v>
       </c>
@@ -45972,26 +46318,26 @@
         <v>190</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="26.4">
+    <row r="22" spans="2:4" ht="25.85">
       <c r="B22" s="2">
         <v>18</v>
       </c>
       <c r="C22" s="84" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D22" s="86" t="s">
-        <v>281</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" ht="26.4">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" ht="25.85">
       <c r="B23" s="2">
         <v>19</v>
       </c>
       <c r="C23" s="84" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="D23" s="86" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
     </row>
     <row r="24" spans="2:4">
@@ -46009,7 +46355,7 @@
       <c r="C26" s="84"/>
       <c r="D26" s="70"/>
     </row>
-    <row r="27" spans="2:4" ht="13.8" thickBot="1">
+    <row r="27" spans="2:4" ht="13.6" thickBot="1">
       <c r="B27" s="4"/>
       <c r="C27" s="85"/>
       <c r="D27" s="6"/>
@@ -46018,5 +46364,8 @@
   <phoneticPr fontId="2"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <headerFooter>
+    <oddHeader>&amp;C&amp;"Calibri"&amp;10&amp;KFF0000 CONFIDENTIAL&amp;1#_x000D_</oddHeader>
+  </headerFooter>
 </worksheet>
 </file>
--- a/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_C_MCBW-CSTD-0-01-B-C0.xlsx
+++ b/src/PE1VM1/App/MET/IpcApplication/Vom/Alert/matrix/scc/alert_C_MCBW-CSTD-0-01-B-C0.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="26731"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\work\10_mcu\19epfv3_mcu_app_mainline\src\IpcApplication\Vom\Alert\matrix\scc\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\_JPlaptop\BEV_MCU\git_v043_AlertFix\src\PE1VM1\App\MET\IpcApplication\Vom\Alert\matrix\scc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D63821D-3305-424D-99AB-7673F383CE9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3124638F-FDFE-459A-B295-9C2705AD98D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-7575" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-14265" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="表紙（承認欄）" sheetId="12" r:id="rId1"/>
@@ -674,7 +674,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2611" uniqueCount="317">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2616" uniqueCount="319">
   <si>
     <t>更新履歴</t>
     <phoneticPr fontId="2"/>
@@ -2612,9 +2612,6 @@
     <t>×</t>
   </si>
   <si>
-    <t>○</t>
-  </si>
-  <si>
     <t>MALFUNC_RW</t>
   </si>
   <si>
@@ -2809,10 +2806,6 @@
   </si>
   <si>
     <t>なし</t>
-    <phoneticPr fontId="2"/>
-  </si>
-  <si>
-    <t>MCMW</t>
     <phoneticPr fontId="2"/>
   </si>
   <si>
@@ -3184,9 +3177,6 @@
     <phoneticPr fontId="2"/>
   </si>
   <si>
-    <t>(株)NTTデータMSE</t>
-  </si>
-  <si>
     <t>承認</t>
     <rPh sb="0" eb="2">
       <t>ショウニン</t>
@@ -3318,6 +3308,34 @@
     <t>品質総点検(R4)：Alert設計書の修正対応
 [C_MCBW]シート
 ・数式の変更(AU8、AU10、AU11)</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>(株)デンソー</t>
+  </si>
+  <si>
+    <t>1.0.2</t>
+    <phoneticPr fontId="2"/>
+  </si>
+  <si>
+    <t>DTPH Kiko</t>
+  </si>
+  <si>
+    <t>－</t>
+  </si>
+  <si>
+    <t>BEVシス検ADAS
+課題対応（BEV3CDCMET-2941）
+[Matrix]シート
+・RWの記載を変更（○→ー）
+[CH_Design]シート
+・RWの記載を変更（MCMW→ー）</t>
+    <rPh sb="11" eb="13">
+      <t>カダイ</t>
+    </rPh>
+    <rPh sb="13" eb="15">
+      <t>タイオウ</t>
+    </rPh>
     <phoneticPr fontId="2"/>
   </si>
 </sst>
@@ -3696,7 +3714,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="84">
+  <borders count="85">
     <border>
       <left/>
       <right/>
@@ -4781,6 +4799,19 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -4793,7 +4824,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="329">
+  <cellXfs count="334">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -5589,6 +5620,21 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="83" xfId="0" applyNumberFormat="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="84" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="62" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="63" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="18" fillId="0" borderId="79" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="27" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5598,6 +5644,9 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="31" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="25" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -5622,9 +5671,6 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="76" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="12" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="11" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6070,16 +6116,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>38</xdr:col>
-      <xdr:colOff>100782</xdr:colOff>
+      <xdr:colOff>134399</xdr:colOff>
       <xdr:row>55</xdr:row>
-      <xdr:rowOff>100782</xdr:rowOff>
+      <xdr:rowOff>103957</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="図 5">
+        <xdr:cNvPr id="7" name="図 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{31CE7A3A-2738-4994-8F8C-FD8C42419C6A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{744994A1-8705-5B40-E112-AEE9E5B9B6EF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -6095,8 +6141,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5667375" y="8420100"/>
-          <a:ext cx="586557" cy="586557"/>
+          <a:off x="5098676" y="8157882"/>
+          <a:ext cx="571429" cy="571429"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -9365,8 +9411,8 @@
       </xdr:nvGrpSpPr>
       <xdr:grpSpPr>
         <a:xfrm>
-          <a:off x="33214235" y="9749118"/>
-          <a:ext cx="15466213" cy="7724221"/>
+          <a:off x="29984700" y="9544050"/>
+          <a:ext cx="13842294" cy="7450051"/>
           <a:chOff x="29718000" y="9666514"/>
           <a:chExt cx="13839119" cy="7508108"/>
         </a:xfrm>
@@ -9511,17 +9557,17 @@
       <sheetName val="４．ナビモデル"/>
       <sheetName val="３．サウンドモデル"/>
       <sheetName val="２．ラジオモデル"/>
+      <sheetName val="1.概述"/>
       <sheetName val="V200複合試験_担当分け_(2)1"/>
       <sheetName val="Spec_List_(19MC-DCM)_1"/>
       <sheetName val="Cooling_Unit"/>
-      <sheetName val="1.概述"/>
       <sheetName val="OpenIssueList"/>
-      <sheetName val="PullDown"/>
       <sheetName val="ECU基盤"/>
       <sheetName val="Name2"/>
       <sheetName val="Name3"/>
       <sheetName val="Company"/>
       <sheetName val="Name"/>
+      <sheetName val="PullDown"/>
       <sheetName val="エンジン型式"/>
       <sheetName val="分类数据"/>
       <sheetName val="index"/>
@@ -9553,6 +9599,37 @@
       <sheetName val="改訂履歴"/>
       <sheetName val="Sheet1"/>
       <sheetName val="⑥フューエル"/>
+      <sheetName val="STEP1-Definition"/>
+      <sheetName val="No.31"/>
+      <sheetName val="階層一覧"/>
+      <sheetName val="测试计划"/>
+      <sheetName val="2.2.4_起動終了時"/>
+      <sheetName val="全戻りﾊﾞｸﾞ"/>
+      <sheetName val="DataShare"/>
+      <sheetName val="ＯＰＭ設備"/>
+      <sheetName val="償却計算"/>
+      <sheetName val="技術費"/>
+      <sheetName val="消耗材"/>
+      <sheetName val="生産用消耗工具費"/>
+      <sheetName val="投資込みＭＪ原価"/>
+      <sheetName val="ＭＪ加工費"/>
+      <sheetName val="仕損根拠"/>
+      <sheetName val="DetailSequence"/>
+      <sheetName val="ERRＩＤ90"/>
+      <sheetName val="vocabulary"/>
+      <sheetName val="Calibration"/>
+      <sheetName val="CVBS"/>
+      <sheetName val="RGB"/>
+      <sheetName val="調査シート"/>
+      <sheetName val="SCH"/>
+      <sheetName val="发行控制"/>
+      <sheetName val="Vibrate test"/>
+      <sheetName val="Data"/>
+      <sheetName val="注釈"/>
+      <sheetName val="仕向け決定用情報取得(GM250)"/>
+      <sheetName val="付録①（GM用）"/>
+      <sheetName val="Data.Share"/>
+      <sheetName val="Func.Share"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
@@ -9633,10 +9710,10 @@
       <sheetData sheetId="57" refreshError="1"/>
       <sheetData sheetId="58" refreshError="1"/>
       <sheetData sheetId="59" refreshError="1"/>
-      <sheetData sheetId="60"/>
+      <sheetData sheetId="60" refreshError="1"/>
       <sheetData sheetId="61"/>
       <sheetData sheetId="62"/>
-      <sheetData sheetId="63" refreshError="1"/>
+      <sheetData sheetId="63"/>
       <sheetData sheetId="64" refreshError="1"/>
       <sheetData sheetId="65" refreshError="1"/>
       <sheetData sheetId="66" refreshError="1"/>
@@ -9675,6 +9752,37 @@
       <sheetData sheetId="99" refreshError="1"/>
       <sheetData sheetId="100" refreshError="1"/>
       <sheetData sheetId="101" refreshError="1"/>
+      <sheetData sheetId="102" refreshError="1"/>
+      <sheetData sheetId="103" refreshError="1"/>
+      <sheetData sheetId="104" refreshError="1"/>
+      <sheetData sheetId="105" refreshError="1"/>
+      <sheetData sheetId="106" refreshError="1"/>
+      <sheetData sheetId="107" refreshError="1"/>
+      <sheetData sheetId="108" refreshError="1"/>
+      <sheetData sheetId="109" refreshError="1"/>
+      <sheetData sheetId="110" refreshError="1"/>
+      <sheetData sheetId="111" refreshError="1"/>
+      <sheetData sheetId="112" refreshError="1"/>
+      <sheetData sheetId="113" refreshError="1"/>
+      <sheetData sheetId="114" refreshError="1"/>
+      <sheetData sheetId="115" refreshError="1"/>
+      <sheetData sheetId="116" refreshError="1"/>
+      <sheetData sheetId="117" refreshError="1"/>
+      <sheetData sheetId="118" refreshError="1"/>
+      <sheetData sheetId="119" refreshError="1"/>
+      <sheetData sheetId="120" refreshError="1"/>
+      <sheetData sheetId="121" refreshError="1"/>
+      <sheetData sheetId="122" refreshError="1"/>
+      <sheetData sheetId="123" refreshError="1"/>
+      <sheetData sheetId="124" refreshError="1"/>
+      <sheetData sheetId="125" refreshError="1"/>
+      <sheetData sheetId="126" refreshError="1"/>
+      <sheetData sheetId="127" refreshError="1"/>
+      <sheetData sheetId="128" refreshError="1"/>
+      <sheetData sheetId="129" refreshError="1"/>
+      <sheetData sheetId="130" refreshError="1"/>
+      <sheetData sheetId="131" refreshError="1"/>
+      <sheetData sheetId="132" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -9813,12 +9921,49 @@
       <sheetName val="Config - dspmgr"/>
       <sheetName val="凡例・注記記載用"/>
       <sheetName val="入力パラメータ"/>
-      <sheetName val="原紙"/>
       <sheetName val="マスタテーブル登録データ"/>
       <sheetName val="記入シート"/>
+      <sheetName val="原紙"/>
       <sheetName val="format"/>
       <sheetName val="検査シート"/>
       <sheetName val="1.概述"/>
+      <sheetName val="InterFace"/>
+      <sheetName val="集計表"/>
+      <sheetName val="vocabulary"/>
+      <sheetName val="Calibration"/>
+      <sheetName val="CVBS"/>
+      <sheetName val="RGB"/>
+      <sheetName val="DetailSequence"/>
+      <sheetName val="日程"/>
+      <sheetName val="進捗"/>
+      <sheetName val="印刷"/>
+      <sheetName val="★ONS_MSG_list"/>
+      <sheetName val="Defined Layout Screen_Ver.0.6"/>
+      <sheetName val="ｲﾝﾊﾟｸﾄ影響台数集計表"/>
+      <sheetName val="実勢(売上)台数表"/>
+      <sheetName val="月別企画台数表"/>
+      <sheetName val="プロジェクト一覧表(現行)"/>
+      <sheetName val="限界利益表(半期別)"/>
+      <sheetName val="機種マスタ"/>
+      <sheetName val="機種ﾏｽﾀ（他車）"/>
+      <sheetName val="売上高表(半期別)"/>
+      <sheetName val="地点情報データ応答"/>
+      <sheetName val="階層一覧"/>
+      <sheetName val="リソーセス算出"/>
+      <sheetName val="定義"/>
+      <sheetName val="ドメイン一覧"/>
+      <sheetName val="変更区分一覧"/>
+      <sheetName val="難易度量一覧"/>
+      <sheetName val="ユーザ一覧"/>
+      <sheetName val="Normal(Mark)"/>
+      <sheetName val="リストデータ"/>
+      <sheetName val="②P071中計　工数パターン1312更新"/>
+      <sheetName val="FBtbl"/>
+      <sheetName val="R0-10表紙"/>
+      <sheetName val="入力規則"/>
+      <sheetName val="#REF"/>
+      <sheetName val="Contents"/>
+      <sheetName val="選択肢"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
@@ -9962,6 +10107,43 @@
       <sheetData sheetId="132" refreshError="1"/>
       <sheetData sheetId="133" refreshError="1"/>
       <sheetData sheetId="134" refreshError="1"/>
+      <sheetData sheetId="135" refreshError="1"/>
+      <sheetData sheetId="136" refreshError="1"/>
+      <sheetData sheetId="137" refreshError="1"/>
+      <sheetData sheetId="138" refreshError="1"/>
+      <sheetData sheetId="139" refreshError="1"/>
+      <sheetData sheetId="140" refreshError="1"/>
+      <sheetData sheetId="141" refreshError="1"/>
+      <sheetData sheetId="142" refreshError="1"/>
+      <sheetData sheetId="143" refreshError="1"/>
+      <sheetData sheetId="144" refreshError="1"/>
+      <sheetData sheetId="145" refreshError="1"/>
+      <sheetData sheetId="146" refreshError="1"/>
+      <sheetData sheetId="147" refreshError="1"/>
+      <sheetData sheetId="148" refreshError="1"/>
+      <sheetData sheetId="149" refreshError="1"/>
+      <sheetData sheetId="150" refreshError="1"/>
+      <sheetData sheetId="151" refreshError="1"/>
+      <sheetData sheetId="152" refreshError="1"/>
+      <sheetData sheetId="153" refreshError="1"/>
+      <sheetData sheetId="154" refreshError="1"/>
+      <sheetData sheetId="155" refreshError="1"/>
+      <sheetData sheetId="156" refreshError="1"/>
+      <sheetData sheetId="157" refreshError="1"/>
+      <sheetData sheetId="158" refreshError="1"/>
+      <sheetData sheetId="159" refreshError="1"/>
+      <sheetData sheetId="160" refreshError="1"/>
+      <sheetData sheetId="161" refreshError="1"/>
+      <sheetData sheetId="162" refreshError="1"/>
+      <sheetData sheetId="163" refreshError="1"/>
+      <sheetData sheetId="164" refreshError="1"/>
+      <sheetData sheetId="165" refreshError="1"/>
+      <sheetData sheetId="166" refreshError="1"/>
+      <sheetData sheetId="167" refreshError="1"/>
+      <sheetData sheetId="168" refreshError="1"/>
+      <sheetData sheetId="169" refreshError="1"/>
+      <sheetData sheetId="170" refreshError="1"/>
+      <sheetData sheetId="171" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -10143,10 +10325,10 @@
       <sheetName val="CPF"/>
       <sheetName val="編集"/>
       <sheetName val="PAIData"/>
+      <sheetName val="⑪1ﾊﾞﾘｴｰｼｮﾝ(16LX)△１"/>
       <sheetName val="NCastalone"/>
       <sheetName val="dongia (2)"/>
       <sheetName val="Volumes"/>
-      <sheetName val="⑪1ﾊﾞﾘｴｰｼｮﾝ(16LX)△１"/>
       <sheetName val="加工費"/>
       <sheetName val="車両仕様 嗼1嗼1噌1鲌"/>
       <sheetName val="車両仕様 勜+勜+匬+鲌"/>
@@ -10156,8 +10338,8 @@
       <sheetName val="Y230"/>
       <sheetName val="MASTER"/>
       <sheetName val="設定"/>
+      <sheetName val="電子ﾎﾞﾘｭｰﾑ設定値（740Nと同一）"/>
       <sheetName val="⑥フューエル"/>
-      <sheetName val="電子ﾎﾞﾘｭｰﾑ設定値（740Nと同一）"/>
       <sheetName val="ﾌﾟﾙﾀﾞｳﾝﾒﾆｭｰ"/>
       <sheetName val="設品表01-3-23作成"/>
       <sheetName val="wire"/>
@@ -10173,25 +10355,24 @@
       <sheetName val="610L611L品番一覧"/>
       <sheetName val="【Input】見積基礎情報（海外生産分)"/>
       <sheetName val="IM-P-L-JB "/>
-      <sheetName val="797T輸入部品リスト"/>
-      <sheetName val="テーブル"/>
-      <sheetName val="Master Updated(517)"/>
-      <sheetName val="４-２．151項目累積（日本）"/>
-      <sheetName val="５-２．151項目累積（北米）"/>
-      <sheetName val="５-１．151項目詳細（北米）"/>
-      <sheetName val="545N仕様ﾗﾌ2"/>
-      <sheetName val="商品力向上"/>
-      <sheetName val="OP-PD"/>
-      <sheetName val="６２３Ｔ"/>
+      <sheetName val="RMBSS's Triggered"/>
+      <sheetName val="_"/>
       <sheetName val="Main 2"/>
       <sheetName val="Datasheet from R. Hinds"/>
-      <sheetName val="GMT900 IPC"/>
+      <sheetName val="545N仕様ﾗﾌ2"/>
+      <sheetName val="Master Updated(517)"/>
+      <sheetName val="６２３Ｔ"/>
+      <sheetName val="商品力向上"/>
+      <sheetName val="ED AND EDOV"/>
       <sheetName val="HORAS_TRAB"/>
       <sheetName val="Resumo_Corolla"/>
       <sheetName val="GASTOS_COROLLA"/>
-      <sheetName val="CALC"/>
-      <sheetName val="ﾘｽﾄ候補"/>
-      <sheetName val="ｺｰﾄﾞ表"/>
+      <sheetName val="④要素記号一覧表"/>
+      <sheetName val="START"/>
+      <sheetName val="Blue Flag"/>
+      <sheetName val="Calc Sheet Budget"/>
+      <sheetName val="見積一覧（１案）"/>
+      <sheetName val="部品"/>
       <sheetName val="①評価項目_メーカー"/>
       <sheetName val="車両仕様_x005f_x0000_4__x005f_x0000__x005f_x0011__x00"/>
       <sheetName val="車両仕様4__x005f_x0000__x005f_x0011__x005f_x0000_"/>
@@ -10218,16 +10399,9 @@
       <sheetName val="車両仕様_4___x005f_x005f_x005f_x005f_x005f_x005f_x001"/>
       <sheetName val="車両仕様4___x005f_x005f_x005f_x005f_x005f_x005f_x0011"/>
       <sheetName val="EFFY_MAZDA"/>
-      <sheetName val="ﾌﾟﾙﾀﾞｳﾝﾒﾆｭｰ用ｺｰﾄﾞ表"/>
-      <sheetName val="_"/>
-      <sheetName val="RMBSS's Triggered"/>
-      <sheetName val="ED AND EDOV"/>
-      <sheetName val="④要素記号一覧表"/>
-      <sheetName val="START"/>
-      <sheetName val="Blue Flag"/>
-      <sheetName val="Calc Sheet Budget"/>
-      <sheetName val="見積一覧（１案）"/>
-      <sheetName val="部品"/>
+      <sheetName val="４-２．151項目累積（日本）"/>
+      <sheetName val="５-２．151項目累積（北米）"/>
+      <sheetName val="５-１．151項目詳細（北米）"/>
       <sheetName val="sebelumCR"/>
       <sheetName val="08TMME"/>
       <sheetName val="VCPT"/>
@@ -10237,6 +10411,14 @@
       <sheetName val="WIP Cal Sheet"/>
       <sheetName val="Pricing overview"/>
       <sheetName val="駆動系1"/>
+      <sheetName val="797T輸入部品リスト"/>
+      <sheetName val="テーブル"/>
+      <sheetName val="OP-PD"/>
+      <sheetName val="GMT900 IPC"/>
+      <sheetName val="CALC"/>
+      <sheetName val="ﾘｽﾄ候補"/>
+      <sheetName val="ｺｰﾄﾞ表"/>
+      <sheetName val="ﾌﾟﾙﾀﾞｳﾝﾒﾆｭｰ用ｺｰﾄﾞ表"/>
       <sheetName val="393.N"/>
       <sheetName val="CæÊ _x0015_ Op"/>
       <sheetName val="ƒƒCƒ“‰æ–Ê _x0015_ Op"/>
@@ -10256,6 +10438,10 @@
       <sheetName val="車両仕様_ᵣ逰ᵣ邀ᵣ郰ᵣ"/>
       <sheetName val="他"/>
       <sheetName val="part"/>
+      <sheetName val="415T原"/>
+      <sheetName val="PAC14"/>
+      <sheetName val="部品表"/>
+      <sheetName val="■07中期明細雛形"/>
       <sheetName val="Vectra"/>
       <sheetName val="PRADO"/>
       <sheetName val="Previous"/>
@@ -10295,10 +10481,6 @@
       <sheetName val="OTHERS x620"/>
       <sheetName val="Ref"/>
       <sheetName val="TOTAL P2"/>
-      <sheetName val="415T原"/>
-      <sheetName val="PAC14"/>
-      <sheetName val="部品表"/>
-      <sheetName val="■07中期明細雛形"/>
       <sheetName val="BUYERS"/>
       <sheetName val="Status"/>
       <sheetName val="PR"/>
@@ -11286,18 +11468,18 @@
       <sheetName val="SUM"/>
       <sheetName val="ﾄﾗｯｸ"/>
       <sheetName val="00"/>
+      <sheetName val="追加検討（調光外部出力）"/>
+      <sheetName val="vocabulary"/>
+      <sheetName val="Calibration"/>
+      <sheetName val="CVBS"/>
+      <sheetName val="RGB"/>
+      <sheetName val="option"/>
       <sheetName val="課題管理"/>
       <sheetName val="C-55227AB"/>
       <sheetName val="Data Definition"/>
       <sheetName val="FC_まとめる"/>
-      <sheetName val="vocabulary"/>
-      <sheetName val="Calibration"/>
-      <sheetName val="CVBS"/>
-      <sheetName val="RGB"/>
       <sheetName val="車両仕様_4___x0011__x00"/>
       <sheetName val="ドメインリスト"/>
-      <sheetName val="option"/>
-      <sheetName val="追加検討（調光外部出力）"/>
       <sheetName val="入力規則"/>
       <sheetName val="Inf"/>
       <sheetName val="#REF!"/>
@@ -11388,8 +11570,29 @@
       <sheetName val="入力LIST"/>
       <sheetName val="パラメータ一覧(AXSS.AXCS)"/>
       <sheetName val="設定値定義"/>
+      <sheetName val="リストデータ"/>
+      <sheetName val="All"/>
+      <sheetName val="58831-06360"/>
+      <sheetName val="1999.4"/>
+      <sheetName val="車両仕様 _x005f_x0000__x005f_x0000__x005f_x000a__x000"/>
+      <sheetName val="車両仕様_x005f_x0000_ῃ_x005f_x0000__x005f_x0014__x000"/>
+      <sheetName val="車両仕様_x005f_x0000__x005f_x0000__x005f_x0000__x0000"/>
+      <sheetName val="車両仕様_x005f_x0000_ῆ玐ῆꆠῨ"/>
+      <sheetName val="車両仕様4?_x005f_x0000__x005f_x0000__x005f_x0000_"/>
+      <sheetName val="SHEET  car no"/>
       <sheetName val="車両仕様????帅?"/>
       <sheetName val="Net Price Position _ Sheet 1"/>
+      <sheetName val="Packing_List2"/>
+      <sheetName val="Packing_List"/>
+      <sheetName val="Calculation_PS"/>
+      <sheetName val="Customer_behaver"/>
+      <sheetName val="Seat_Assy_Tool_Tracking"/>
+      <sheetName val="Stock_in_Trade1"/>
+      <sheetName val="Packing_List21"/>
+      <sheetName val="Packing_List1"/>
+      <sheetName val="Calculation_PS1"/>
+      <sheetName val="Customer_behaver1"/>
+      <sheetName val="Seat_Assy_Tool_Tracking1"/>
       <sheetName val="POs"/>
       <sheetName val="計算式"/>
       <sheetName val="工管合計"/>
@@ -12913,15 +13116,9 @@
       <sheetName val="5"/>
       <sheetName val="確認ｼｰﾄ(TBU)"/>
       <sheetName val="Sheet1 (2)"/>
-      <sheetName val="SHEET  car no"/>
       <sheetName val="サイクル"/>
       <sheetName val="特殊サイクル一覧"/>
       <sheetName val="カメラ"/>
-      <sheetName val="車両仕様 _x005f_x0000__x005f_x0000__x005f_x000a__x000"/>
-      <sheetName val="車両仕様_x005f_x0000_ῃ_x005f_x0000__x005f_x0014__x000"/>
-      <sheetName val="車両仕様_x005f_x0000__x005f_x0000__x005f_x0000__x0000"/>
-      <sheetName val="車両仕様_x005f_x0000_ῆ玐ῆꆠῨ"/>
-      <sheetName val="車両仕様4?_x005f_x0000__x005f_x0000__x005f_x0000_"/>
       <sheetName val="台数"/>
       <sheetName val="MET397D-25"/>
       <sheetName val="集計表"/>
@@ -12930,21 +13127,6 @@
       <sheetName val="Ｓｉ問連"/>
       <sheetName val="アップロード系(2)"/>
       <sheetName val="エンジン型式"/>
-      <sheetName val="リストデータ"/>
-      <sheetName val="All"/>
-      <sheetName val="58831-06360"/>
-      <sheetName val="1999.4"/>
-      <sheetName val="Packing_List2"/>
-      <sheetName val="Packing_List"/>
-      <sheetName val="Calculation_PS"/>
-      <sheetName val="Customer_behaver"/>
-      <sheetName val="Seat_Assy_Tool_Tracking"/>
-      <sheetName val="Stock_in_Trade1"/>
-      <sheetName val="Packing_List21"/>
-      <sheetName val="Packing_List1"/>
-      <sheetName val="Calculation_PS1"/>
-      <sheetName val="Customer_behaver1"/>
-      <sheetName val="Seat_Assy_Tool_Tracking1"/>
       <sheetName val="Index"/>
       <sheetName val="Defined Layout Screen_Ver.0.6"/>
       <sheetName val="９ｘ"/>
@@ -12956,6 +13138,185 @@
       <sheetName val="config"/>
       <sheetName val="地点情報データ応答"/>
       <sheetName val="Par"/>
+      <sheetName val="Calcul"/>
+      <sheetName val="ETC機能判定"/>
+      <sheetName val="ETCメニュー"/>
+      <sheetName val="登録情報表示"/>
+      <sheetName val="ETC設定"/>
+      <sheetName val="履歴情報表示"/>
+      <sheetName val="履歴情報詳細表示"/>
+      <sheetName val="メニュー２"/>
+      <sheetName val="割込み(Disp)"/>
+      <sheetName val="割込み(Navi)"/>
+      <sheetName val="走行強制状態変化"/>
+      <sheetName val="入力パラメータ"/>
+      <sheetName val="DetailSequence"/>
+      <sheetName val="InterFace"/>
+      <sheetName val="FBtbl"/>
+      <sheetName val="リスト画面"/>
+      <sheetName val="特殊画面"/>
+      <sheetName val="入力画面"/>
+      <sheetName val="メッセージ受信開始"/>
+      <sheetName val="Mark"/>
+      <sheetName val="Contents"/>
+      <sheetName val="車両仕様4_ "/>
+      <sheetName val="改正履歴"/>
+      <sheetName val="リスト選択用"/>
+      <sheetName val="变更履历"/>
+      <sheetName val="Menu List"/>
+      <sheetName val="ドメイン一覧"/>
+      <sheetName val="検査シート"/>
+      <sheetName val="Cover"/>
+      <sheetName val="MIS REPORT "/>
+      <sheetName val="（別紙5-1）PP02簡素化"/>
+      <sheetName val="universal"/>
+      <sheetName val="Cost Casting"/>
+      <sheetName val="paint mtrl"/>
+      <sheetName val="corolla_095W_"/>
+      <sheetName val="dyna"/>
+      <sheetName val="FC"/>
+      <sheetName val="★ONS_MSG_list"/>
+      <sheetName val="ﾕｰｻﾞｰ設定"/>
+      <sheetName val="同行评审"/>
+      <sheetName val="5.心配点抽出-0"/>
+      <sheetName val="0.表紙"/>
+      <sheetName val="1._概要"/>
+      <sheetName val="4 選局"/>
+      <sheetName val="定数"/>
+      <sheetName val="Case 21_1"/>
+      <sheetName val="96期(川崎)"/>
+      <sheetName val="ORDSHP"/>
+      <sheetName val="B"/>
+      <sheetName val="Blue_Flag3"/>
+      <sheetName val="Calc_Sheet_Budget3"/>
+      <sheetName val="_PART_479W_LHD3"/>
+      <sheetName val="_PART_MYY5A3"/>
+      <sheetName val="393_N3"/>
+      <sheetName val="WIP_Cal_Sheet3"/>
+      <sheetName val="Pricing_overview3"/>
+      <sheetName val="Lookup_Table3"/>
+      <sheetName val="promo_lists_20113"/>
+      <sheetName val="車両仕様_嗼1嗼1噌1鲌3"/>
+      <sheetName val="車両仕様_勜+勜+匬+鲌3"/>
+      <sheetName val="EquipmentTrimming_Cabin_NS3"/>
+      <sheetName val="Reference_3"/>
+      <sheetName val="車両仕様__x005f_x0000__x005f_x0000_?_x005f_x0012_?瞳?3"/>
+      <sheetName val="車両仕様_???_x005f_x0012_?瞳?3"/>
+      <sheetName val="160th_NPCC_Nov'103"/>
+      <sheetName val="RMBSS's_Triggered3"/>
+      <sheetName val="車両仕様?4???_??3"/>
+      <sheetName val="車両仕様_???_?瞳?3"/>
+      <sheetName val="車両仕様???ꎨ_窉瞳㾐3"/>
+      <sheetName val="車両仕様?4??_?3"/>
+      <sheetName val="車両仕様4??_?3"/>
+      <sheetName val="車両仕様____瞳_3"/>
+      <sheetName val="車両仕様______瞳_3"/>
+      <sheetName val="車両仕様_4______3"/>
+      <sheetName val="車両仕様___ꎨ_窉瞳㾐3"/>
+      <sheetName val="車両仕様_4____3"/>
+      <sheetName val="車両仕様4____3"/>
+      <sheetName val="PRICE_LIST3"/>
+      <sheetName val="Loss_Time3"/>
+      <sheetName val="Price_range_IT3"/>
+      <sheetName val="Avensis+d_seg__in_&amp;_out_of_UK+3"/>
+      <sheetName val="#ofclose__xl3"/>
+      <sheetName val="Annexes_toutes_bases3"/>
+      <sheetName val="DON_GIA3"/>
+      <sheetName val="CHITIET_VL-NC3"/>
+      <sheetName val="TONGKE3p_3"/>
+      <sheetName val="TOTAL_P23"/>
+      <sheetName val="2_-_Summary3"/>
+      <sheetName val="IPOTESI_PIANO_STATICA3"/>
+      <sheetName val="make_up3"/>
+      <sheetName val="車両仕様_???_x005f_x005f_x005f_x0012_?瞳?3"/>
+      <sheetName val="調達担当者(06_2～)3"/>
+      <sheetName val="車両仕様__x005f_x0000__2"/>
+      <sheetName val="車両仕様_x005f_x0000__N2"/>
+      <sheetName val="車両仕様___x005f_x0012_2"/>
+      <sheetName val="車両仕様__x005f_x005f_x2"/>
+      <sheetName val="車両仕様___x005f_x005f_2"/>
+      <sheetName val="05-065_she2"/>
+      <sheetName val="idgr_-_formula2"/>
+      <sheetName val="IDGR_(3)2"/>
+      <sheetName val="IDGR_(2)2"/>
+      <sheetName val="PLIV_(3)2"/>
+      <sheetName val="PLIV_(2)2"/>
+      <sheetName val="PLIV_(template)2"/>
+      <sheetName val="inv_recon2"/>
+      <sheetName val="side_member2"/>
+      <sheetName val="TTC_(FG)2"/>
+      <sheetName val="Sheet1_(3)2"/>
+      <sheetName val="truck_allocation2"/>
+      <sheetName val="Supplier_Price_Check2"/>
+      <sheetName val="$_-_june2"/>
+      <sheetName val="Vios_Cost_Reduction_actual_pro2"/>
+      <sheetName val="RET_PALLET2"/>
+      <sheetName val="Form_A2"/>
+      <sheetName val="NG_SUMMARY2"/>
+      <sheetName val="impact_pallet_and_racks2"/>
+      <sheetName val="Daily_WSD2"/>
+      <sheetName val="ass'y_12'04-05'053"/>
+      <sheetName val="Type_I2"/>
+      <sheetName val="Schedule_PM2"/>
+      <sheetName val="training_forklift2"/>
+      <sheetName val="Budget_by_Category2"/>
+      <sheetName val="investment_tmc_v8_0_34p2"/>
+      <sheetName val="PTD_Activity2"/>
+      <sheetName val="Sample_1PP_2"/>
+      <sheetName val="Open_Ran3"/>
+      <sheetName val="Open_RAN_23"/>
+      <sheetName val="CHIA_KH2"/>
+      <sheetName val="Purch__BP2"/>
+      <sheetName val="車両仕様_____x005f_x005f_x005f_x005f_x0013"/>
+      <sheetName val="車両仕様_____x005f_x005f_x005f_x005f_x0053"/>
+      <sheetName val="ＰＲＥ_NO1"/>
+      <sheetName val="Courier_4x2"/>
+      <sheetName val="Price_Trend2"/>
+      <sheetName val="車両仕様_?_x005f_x0012_?瞳?2"/>
+      <sheetName val="YARIS_HB2"/>
+      <sheetName val="00_KS"/>
+      <sheetName val="PRADO_3Dr_fl2"/>
+      <sheetName val="01_DATA2"/>
+      <sheetName val="Quality_Update2"/>
+      <sheetName val="prior_data"/>
+      <sheetName val="Table_Master"/>
+      <sheetName val="1_概述"/>
+      <sheetName val="Drop-down_Menu_List"/>
+      <sheetName val="Open_Item_List"/>
+      <sheetName val="本修正_DIFF_"/>
+      <sheetName val="Sector_Assignment"/>
+      <sheetName val="BQ_CONVEYOR"/>
+      <sheetName val="IMV_LIST_2003"/>
+      <sheetName val="車両仕様_x005f_x0000_4__x005f_x0000__x005f_x0000___x0"/>
+      <sheetName val="車両仕様__x005f_x0000__x005f_x0000____瞳_"/>
+      <sheetName val="Part_list"/>
+      <sheetName val="INACT797"/>
+      <sheetName val="M1A"/>
+      <sheetName val="OK"/>
+      <sheetName val="??? Pilling upu_S y"/>
+      <sheetName val="ASF INVENTORY"/>
+      <sheetName val="車両仕様_4___x005f_x0013__x0013__x0013__x0013__x0013_"/>
+      <sheetName val="ጀጀ؀ԀЀࠀ᐀Ѐऀ܀̀܀ഀ܀Ԁऀ଀ࠀ_x0000_"/>
+      <sheetName val="CTable"/>
+      <sheetName val="bs is"/>
+      <sheetName val="成績"/>
+      <sheetName val="IT Checklist"/>
+      <sheetName val="ﾊﾟｲﾌﾟ"/>
+      <sheetName val="冷延鋼板"/>
+      <sheetName val="熱延鋼板"/>
+      <sheetName val="他材料費"/>
+      <sheetName val="No.31"/>
+      <sheetName val="コマンド認識, DTMF"/>
+      <sheetName val="CS2_SmcDriverインテグ項目"/>
+      <sheetName val="標準仕様DB"/>
+      <sheetName val="BEEP設定"/>
+      <sheetName val="休日"/>
+      <sheetName val="工数ｺｰﾄﾞﾘｽﾄ"/>
+      <sheetName val="5．キー入力動作説明"/>
+      <sheetName val="日程"/>
+      <sheetName val="進捗"/>
+      <sheetName val="印刷"/>
+      <sheetName val="試験項目_R3小"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0" refreshError="1"/>
@@ -13511,33 +13872,45 @@
       <sheetData sheetId="304" refreshError="1"/>
       <sheetData sheetId="305" refreshError="1"/>
       <sheetData sheetId="306" refreshError="1"/>
-      <sheetData sheetId="307">
+      <sheetData sheetId="307" refreshError="1"/>
+      <sheetData sheetId="308" refreshError="1"/>
+      <sheetData sheetId="309" refreshError="1"/>
+      <sheetData sheetId="310" refreshError="1"/>
+      <sheetData sheetId="311">
         <row r="1">
           <cell r="B1" t="str">
             <v>1</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="308">
+      <sheetData sheetId="312">
         <row r="1">
           <cell r="B1" t="str">
             <v>1</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="309">
+      <sheetData sheetId="313">
         <row r="1">
           <cell r="B1" t="str">
             <v>1</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="310"/>
-      <sheetData sheetId="311"/>
-      <sheetData sheetId="312" refreshError="1"/>
-      <sheetData sheetId="313" refreshError="1"/>
-      <sheetData sheetId="314" refreshError="1"/>
-      <sheetData sheetId="315" refreshError="1"/>
+      <sheetData sheetId="314">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="315">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="316" refreshError="1"/>
       <sheetData sheetId="317" refreshError="1"/>
       <sheetData sheetId="318" refreshError="1"/>
@@ -15109,8 +15482,8 @@
       </sheetData>
       <sheetData sheetId="793">
         <row r="1">
-          <cell r="B1" t="str">
-            <v>1</v>
+          <cell r="A1" t="str">
+            <v>ﾄﾖﾀ自動車株式会社　調達本部　</v>
           </cell>
         </row>
       </sheetData>
@@ -15146,7 +15519,13 @@
       <sheetData sheetId="805" refreshError="1"/>
       <sheetData sheetId="806" refreshError="1"/>
       <sheetData sheetId="807" refreshError="1"/>
-      <sheetData sheetId="808"/>
+      <sheetData sheetId="808">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="809" refreshError="1"/>
       <sheetData sheetId="810" refreshError="1"/>
       <sheetData sheetId="811" refreshError="1"/>
@@ -16109,9 +16488,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1050">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -16333,9 +16712,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1082">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -16354,9 +16733,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1085">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -16683,9 +17062,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1132">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -16774,9 +17153,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1145">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17005,16 +17384,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1178">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1179">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17054,9 +17433,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1185">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17082,9 +17461,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1189">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17103,9 +17482,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1192">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17173,9 +17552,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1202">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17194,16 +17573,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1205">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1206">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17215,16 +17594,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1208">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1209">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17264,9 +17643,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1215">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17292,9 +17671,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1219">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17313,9 +17692,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1222">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17383,9 +17762,9 @@
         </row>
       </sheetData>
       <sheetData sheetId="1232">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17404,16 +17783,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1235">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1236">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17425,16 +17804,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1238">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1239">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17474,16 +17853,16 @@
         </row>
       </sheetData>
       <sheetData sheetId="1245">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
       <sheetData sheetId="1246">
-        <row r="3">
-          <cell r="B3" t="str">
-            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
           </cell>
         </row>
       </sheetData>
@@ -17543,16 +17922,76 @@
       <sheetData sheetId="1294"/>
       <sheetData sheetId="1295" refreshError="1"/>
       <sheetData sheetId="1296" refreshError="1"/>
-      <sheetData sheetId="1297"/>
-      <sheetData sheetId="1298"/>
-      <sheetData sheetId="1299"/>
-      <sheetData sheetId="1300"/>
-      <sheetData sheetId="1301"/>
-      <sheetData sheetId="1302"/>
-      <sheetData sheetId="1303"/>
-      <sheetData sheetId="1304"/>
-      <sheetData sheetId="1305"/>
-      <sheetData sheetId="1306"/>
+      <sheetData sheetId="1297">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1298">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1299">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1300">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1301">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1302">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1303">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1304">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1305">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1306">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1307" refreshError="1"/>
       <sheetData sheetId="1308" refreshError="1"/>
       <sheetData sheetId="1309" refreshError="1"/>
@@ -17562,13 +18001,13 @@
       <sheetData sheetId="1313" refreshError="1"/>
       <sheetData sheetId="1314" refreshError="1"/>
       <sheetData sheetId="1315" refreshError="1"/>
-      <sheetData sheetId="1316"/>
+      <sheetData sheetId="1316" refreshError="1"/>
       <sheetData sheetId="1317" refreshError="1"/>
       <sheetData sheetId="1318" refreshError="1"/>
       <sheetData sheetId="1319" refreshError="1"/>
       <sheetData sheetId="1320" refreshError="1"/>
       <sheetData sheetId="1321" refreshError="1"/>
-      <sheetData sheetId="1322" refreshError="1"/>
+      <sheetData sheetId="1322"/>
       <sheetData sheetId="1323" refreshError="1"/>
       <sheetData sheetId="1324" refreshError="1"/>
       <sheetData sheetId="1325" refreshError="1"/>
@@ -17663,39 +18102,33 @@
       <sheetData sheetId="1414" refreshError="1"/>
       <sheetData sheetId="1415" refreshError="1"/>
       <sheetData sheetId="1416" refreshError="1"/>
-      <sheetData sheetId="1417"/>
+      <sheetData sheetId="1417" refreshError="1"/>
       <sheetData sheetId="1418" refreshError="1"/>
       <sheetData sheetId="1419" refreshError="1"/>
       <sheetData sheetId="1420" refreshError="1"/>
       <sheetData sheetId="1421" refreshError="1"/>
       <sheetData sheetId="1422" refreshError="1"/>
-      <sheetData sheetId="1423"/>
-      <sheetData sheetId="1424"/>
-      <sheetData sheetId="1425"/>
-      <sheetData sheetId="1426"/>
+      <sheetData sheetId="1423" refreshError="1"/>
+      <sheetData sheetId="1424" refreshError="1"/>
+      <sheetData sheetId="1425" refreshError="1"/>
+      <sheetData sheetId="1426" refreshError="1"/>
       <sheetData sheetId="1427"/>
-      <sheetData sheetId="1428"/>
+      <sheetData sheetId="1428" refreshError="1"/>
       <sheetData sheetId="1429"/>
       <sheetData sheetId="1430"/>
       <sheetData sheetId="1431"/>
       <sheetData sheetId="1432"/>
       <sheetData sheetId="1433"/>
-      <sheetData sheetId="1434" refreshError="1"/>
-      <sheetData sheetId="1435">
-        <row r="3">
-          <cell r="C3" t="str">
-            <v>2022年</v>
-          </cell>
-        </row>
-      </sheetData>
+      <sheetData sheetId="1434"/>
+      <sheetData sheetId="1435"/>
       <sheetData sheetId="1436"/>
       <sheetData sheetId="1437"/>
       <sheetData sheetId="1438"/>
       <sheetData sheetId="1439"/>
-      <sheetData sheetId="1440"/>
-      <sheetData sheetId="1441"/>
-      <sheetData sheetId="1442"/>
-      <sheetData sheetId="1443"/>
+      <sheetData sheetId="1440" refreshError="1"/>
+      <sheetData sheetId="1441" refreshError="1"/>
+      <sheetData sheetId="1442" refreshError="1"/>
+      <sheetData sheetId="1443" refreshError="1"/>
       <sheetData sheetId="1444"/>
       <sheetData sheetId="1445"/>
       <sheetData sheetId="1446"/>
@@ -17707,8 +18140,14 @@
       <sheetData sheetId="1452"/>
       <sheetData sheetId="1453"/>
       <sheetData sheetId="1454"/>
-      <sheetData sheetId="1455"/>
-      <sheetData sheetId="1456"/>
+      <sheetData sheetId="1455" refreshError="1"/>
+      <sheetData sheetId="1456">
+        <row r="3">
+          <cell r="C3" t="str">
+            <v>2022年</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1457"/>
       <sheetData sheetId="1458"/>
       <sheetData sheetId="1459"/>
@@ -17788,19 +18227,73 @@
       <sheetData sheetId="1533"/>
       <sheetData sheetId="1534"/>
       <sheetData sheetId="1535"/>
-      <sheetData sheetId="1536"/>
-      <sheetData sheetId="1537"/>
+      <sheetData sheetId="1536">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1537">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1538"/>
-      <sheetData sheetId="1539"/>
+      <sheetData sheetId="1539">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1540"/>
-      <sheetData sheetId="1541"/>
-      <sheetData sheetId="1542"/>
-      <sheetData sheetId="1543"/>
+      <sheetData sheetId="1541">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1542">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1543">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1544"/>
-      <sheetData sheetId="1545"/>
+      <sheetData sheetId="1545">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1546"/>
-      <sheetData sheetId="1547"/>
-      <sheetData sheetId="1548"/>
+      <sheetData sheetId="1547">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="1548">
+        <row r="1">
+          <cell r="B1" t="str">
+            <v>1</v>
+          </cell>
+        </row>
+      </sheetData>
       <sheetData sheetId="1549"/>
       <sheetData sheetId="1550"/>
       <sheetData sheetId="1551"/>
@@ -19190,52 +19683,52 @@
       <sheetData sheetId="2935"/>
       <sheetData sheetId="2936"/>
       <sheetData sheetId="2937"/>
-      <sheetData sheetId="2938">
-        <row r="1">
-          <cell r="A1"/>
-        </row>
-      </sheetData>
+      <sheetData sheetId="2938"/>
       <sheetData sheetId="2939"/>
       <sheetData sheetId="2940"/>
       <sheetData sheetId="2941"/>
-      <sheetData sheetId="2942" refreshError="1"/>
-      <sheetData sheetId="2943">
+      <sheetData sheetId="2942"/>
+      <sheetData sheetId="2943"/>
+      <sheetData sheetId="2944"/>
+      <sheetData sheetId="2945"/>
+      <sheetData sheetId="2946"/>
+      <sheetData sheetId="2947"/>
+      <sheetData sheetId="2948"/>
+      <sheetData sheetId="2949"/>
+      <sheetData sheetId="2950"/>
+      <sheetData sheetId="2951"/>
+      <sheetData sheetId="2952"/>
+      <sheetData sheetId="2953"/>
+      <sheetData sheetId="2954"/>
+      <sheetData sheetId="2955"/>
+      <sheetData sheetId="2956"/>
+      <sheetData sheetId="2957"/>
+      <sheetData sheetId="2958"/>
+      <sheetData sheetId="2959">
+        <row r="1">
+          <cell r="A1"/>
+        </row>
+      </sheetData>
+      <sheetData sheetId="2960"/>
+      <sheetData sheetId="2961"/>
+      <sheetData sheetId="2962"/>
+      <sheetData sheetId="2963">
         <row r="1">
           <cell r="B1" t="str">
             <v>文章管理番号</v>
           </cell>
         </row>
       </sheetData>
-      <sheetData sheetId="2944"/>
-      <sheetData sheetId="2945" refreshError="1"/>
-      <sheetData sheetId="2946" refreshError="1"/>
-      <sheetData sheetId="2947" refreshError="1"/>
-      <sheetData sheetId="2948" refreshError="1"/>
-      <sheetData sheetId="2949" refreshError="1"/>
-      <sheetData sheetId="2950" refreshError="1"/>
-      <sheetData sheetId="2951" refreshError="1"/>
-      <sheetData sheetId="2952" refreshError="1"/>
-      <sheetData sheetId="2953" refreshError="1"/>
-      <sheetData sheetId="2954" refreshError="1"/>
-      <sheetData sheetId="2955" refreshError="1"/>
-      <sheetData sheetId="2956" refreshError="1"/>
-      <sheetData sheetId="2957" refreshError="1"/>
-      <sheetData sheetId="2958" refreshError="1"/>
-      <sheetData sheetId="2959" refreshError="1"/>
-      <sheetData sheetId="2960" refreshError="1"/>
-      <sheetData sheetId="2961" refreshError="1"/>
-      <sheetData sheetId="2962" refreshError="1"/>
-      <sheetData sheetId="2963"/>
       <sheetData sheetId="2964"/>
-      <sheetData sheetId="2965"/>
-      <sheetData sheetId="2966"/>
-      <sheetData sheetId="2967"/>
-      <sheetData sheetId="2968"/>
-      <sheetData sheetId="2969"/>
-      <sheetData sheetId="2970"/>
-      <sheetData sheetId="2971"/>
-      <sheetData sheetId="2972"/>
-      <sheetData sheetId="2973"/>
+      <sheetData sheetId="2965" refreshError="1"/>
+      <sheetData sheetId="2966" refreshError="1"/>
+      <sheetData sheetId="2967" refreshError="1"/>
+      <sheetData sheetId="2968" refreshError="1"/>
+      <sheetData sheetId="2969" refreshError="1"/>
+      <sheetData sheetId="2970" refreshError="1"/>
+      <sheetData sheetId="2971" refreshError="1"/>
+      <sheetData sheetId="2972" refreshError="1"/>
+      <sheetData sheetId="2973" refreshError="1"/>
       <sheetData sheetId="2974" refreshError="1"/>
       <sheetData sheetId="2975"/>
       <sheetData sheetId="2976" refreshError="1"/>
@@ -19247,6 +19740,323 @@
       <sheetData sheetId="2982" refreshError="1"/>
       <sheetData sheetId="2983" refreshError="1"/>
       <sheetData sheetId="2984" refreshError="1"/>
+      <sheetData sheetId="2985" refreshError="1"/>
+      <sheetData sheetId="2986" refreshError="1"/>
+      <sheetData sheetId="2987" refreshError="1"/>
+      <sheetData sheetId="2988" refreshError="1"/>
+      <sheetData sheetId="2989" refreshError="1"/>
+      <sheetData sheetId="2990" refreshError="1"/>
+      <sheetData sheetId="2991" refreshError="1"/>
+      <sheetData sheetId="2992" refreshError="1"/>
+      <sheetData sheetId="2993" refreshError="1"/>
+      <sheetData sheetId="2994" refreshError="1"/>
+      <sheetData sheetId="2995" refreshError="1"/>
+      <sheetData sheetId="2996" refreshError="1"/>
+      <sheetData sheetId="2997" refreshError="1"/>
+      <sheetData sheetId="2998" refreshError="1"/>
+      <sheetData sheetId="2999" refreshError="1"/>
+      <sheetData sheetId="3000" refreshError="1"/>
+      <sheetData sheetId="3001" refreshError="1"/>
+      <sheetData sheetId="3002" refreshError="1"/>
+      <sheetData sheetId="3003" refreshError="1"/>
+      <sheetData sheetId="3004" refreshError="1"/>
+      <sheetData sheetId="3005" refreshError="1"/>
+      <sheetData sheetId="3006" refreshError="1"/>
+      <sheetData sheetId="3007" refreshError="1"/>
+      <sheetData sheetId="3008" refreshError="1"/>
+      <sheetData sheetId="3009" refreshError="1"/>
+      <sheetData sheetId="3010" refreshError="1"/>
+      <sheetData sheetId="3011" refreshError="1"/>
+      <sheetData sheetId="3012" refreshError="1"/>
+      <sheetData sheetId="3013" refreshError="1"/>
+      <sheetData sheetId="3014" refreshError="1"/>
+      <sheetData sheetId="3015" refreshError="1"/>
+      <sheetData sheetId="3016" refreshError="1"/>
+      <sheetData sheetId="3017" refreshError="1"/>
+      <sheetData sheetId="3018" refreshError="1"/>
+      <sheetData sheetId="3019" refreshError="1"/>
+      <sheetData sheetId="3020" refreshError="1"/>
+      <sheetData sheetId="3021" refreshError="1"/>
+      <sheetData sheetId="3022" refreshError="1"/>
+      <sheetData sheetId="3023" refreshError="1"/>
+      <sheetData sheetId="3024" refreshError="1"/>
+      <sheetData sheetId="3025" refreshError="1"/>
+      <sheetData sheetId="3026" refreshError="1"/>
+      <sheetData sheetId="3027" refreshError="1"/>
+      <sheetData sheetId="3028" refreshError="1"/>
+      <sheetData sheetId="3029" refreshError="1"/>
+      <sheetData sheetId="3030" refreshError="1"/>
+      <sheetData sheetId="3031" refreshError="1"/>
+      <sheetData sheetId="3032" refreshError="1"/>
+      <sheetData sheetId="3033" refreshError="1"/>
+      <sheetData sheetId="3034"/>
+      <sheetData sheetId="3035"/>
+      <sheetData sheetId="3036"/>
+      <sheetData sheetId="3037"/>
+      <sheetData sheetId="3038"/>
+      <sheetData sheetId="3039"/>
+      <sheetData sheetId="3040"/>
+      <sheetData sheetId="3041"/>
+      <sheetData sheetId="3042"/>
+      <sheetData sheetId="3043"/>
+      <sheetData sheetId="3044"/>
+      <sheetData sheetId="3045"/>
+      <sheetData sheetId="3046"/>
+      <sheetData sheetId="3047"/>
+      <sheetData sheetId="3048"/>
+      <sheetData sheetId="3049"/>
+      <sheetData sheetId="3050"/>
+      <sheetData sheetId="3051"/>
+      <sheetData sheetId="3052"/>
+      <sheetData sheetId="3053"/>
+      <sheetData sheetId="3054"/>
+      <sheetData sheetId="3055"/>
+      <sheetData sheetId="3056"/>
+      <sheetData sheetId="3057"/>
+      <sheetData sheetId="3058"/>
+      <sheetData sheetId="3059"/>
+      <sheetData sheetId="3060"/>
+      <sheetData sheetId="3061"/>
+      <sheetData sheetId="3062"/>
+      <sheetData sheetId="3063"/>
+      <sheetData sheetId="3064"/>
+      <sheetData sheetId="3065"/>
+      <sheetData sheetId="3066"/>
+      <sheetData sheetId="3067"/>
+      <sheetData sheetId="3068"/>
+      <sheetData sheetId="3069"/>
+      <sheetData sheetId="3070"/>
+      <sheetData sheetId="3071"/>
+      <sheetData sheetId="3072"/>
+      <sheetData sheetId="3073"/>
+      <sheetData sheetId="3074"/>
+      <sheetData sheetId="3075"/>
+      <sheetData sheetId="3076"/>
+      <sheetData sheetId="3077">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3078">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3079">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3080">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3081">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3082">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3083">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3084">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3085">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3086">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3087">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3088">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3089">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3090">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3091">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3092">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3093">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3094">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3095">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3096">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3097">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3098">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3099">
+        <row r="3">
+          <cell r="B3" t="str">
+            <v>TOYOTA   TSUSHO  PHILIPPINES CORPORATION</v>
+          </cell>
+        </row>
+      </sheetData>
+      <sheetData sheetId="3100"/>
+      <sheetData sheetId="3101"/>
+      <sheetData sheetId="3102"/>
+      <sheetData sheetId="3103"/>
+      <sheetData sheetId="3104"/>
+      <sheetData sheetId="3105"/>
+      <sheetData sheetId="3106"/>
+      <sheetData sheetId="3107"/>
+      <sheetData sheetId="3108"/>
+      <sheetData sheetId="3109"/>
+      <sheetData sheetId="3110"/>
+      <sheetData sheetId="3111"/>
+      <sheetData sheetId="3112"/>
+      <sheetData sheetId="3113"/>
+      <sheetData sheetId="3114"/>
+      <sheetData sheetId="3115"/>
+      <sheetData sheetId="3116"/>
+      <sheetData sheetId="3117"/>
+      <sheetData sheetId="3118"/>
+      <sheetData sheetId="3119"/>
+      <sheetData sheetId="3120"/>
+      <sheetData sheetId="3121"/>
+      <sheetData sheetId="3122"/>
+      <sheetData sheetId="3123"/>
+      <sheetData sheetId="3124"/>
+      <sheetData sheetId="3125"/>
+      <sheetData sheetId="3126"/>
+      <sheetData sheetId="3127"/>
+      <sheetData sheetId="3128"/>
+      <sheetData sheetId="3129"/>
+      <sheetData sheetId="3130"/>
+      <sheetData sheetId="3131"/>
+      <sheetData sheetId="3132"/>
+      <sheetData sheetId="3133"/>
+      <sheetData sheetId="3134"/>
+      <sheetData sheetId="3135"/>
+      <sheetData sheetId="3136"/>
+      <sheetData sheetId="3137" refreshError="1"/>
+      <sheetData sheetId="3138" refreshError="1"/>
+      <sheetData sheetId="3139" refreshError="1"/>
+      <sheetData sheetId="3140" refreshError="1"/>
+      <sheetData sheetId="3141" refreshError="1"/>
+      <sheetData sheetId="3142" refreshError="1"/>
+      <sheetData sheetId="3143" refreshError="1"/>
+      <sheetData sheetId="3144" refreshError="1"/>
+      <sheetData sheetId="3145" refreshError="1"/>
+      <sheetData sheetId="3146" refreshError="1"/>
+      <sheetData sheetId="3147" refreshError="1"/>
+      <sheetData sheetId="3148" refreshError="1"/>
+      <sheetData sheetId="3149" refreshError="1"/>
+      <sheetData sheetId="3150" refreshError="1"/>
+      <sheetData sheetId="3151" refreshError="1"/>
+      <sheetData sheetId="3152" refreshError="1"/>
+      <sheetData sheetId="3153" refreshError="1"/>
+      <sheetData sheetId="3154" refreshError="1"/>
+      <sheetData sheetId="3155" refreshError="1"/>
+      <sheetData sheetId="3156" refreshError="1"/>
+      <sheetData sheetId="3157" refreshError="1"/>
+      <sheetData sheetId="3158" refreshError="1"/>
+      <sheetData sheetId="3159" refreshError="1"/>
+      <sheetData sheetId="3160" refreshError="1"/>
+      <sheetData sheetId="3161" refreshError="1"/>
+      <sheetData sheetId="3162" refreshError="1"/>
+      <sheetData sheetId="3163" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -19341,17 +20151,62 @@
       <sheetName val="_UnderConst_Analysis"/>
       <sheetName val="アップロード系(2)"/>
       <sheetName val="List"/>
+      <sheetName val="パラメータ設定表"/>
       <sheetName val="別紙7_操作系イベント発生時_"/>
       <sheetName val="別紙11_各競合条件における起動可否_"/>
       <sheetName val="index"/>
-      <sheetName val="パラメータ設定表"/>
+      <sheetName val="入力"/>
+      <sheetName val="415T戟L"/>
+      <sheetName val="No.31"/>
       <sheetName val="改訂履歴"/>
       <sheetName val="リスト"/>
       <sheetName val="ドメイン"/>
       <sheetName val="format"/>
-      <sheetName val="入力"/>
-      <sheetName val="415T戟L"/>
-      <sheetName val="No.31"/>
+      <sheetName val="Navigation"/>
+      <sheetName val="Cover"/>
+      <sheetName val="DataList"/>
+      <sheetName val="変更要件"/>
+      <sheetName val="【石倉編集中】DisplayStateTransitionTa"/>
+      <sheetName val="DetailSequence"/>
+      <sheetName val="R0-10表紙"/>
+      <sheetName val="Calcul"/>
+      <sheetName val="Data"/>
+      <sheetName val="★VarUsed"/>
+      <sheetName val="輝度計算(直線用)"/>
+      <sheetName val="コード_dimautocon"/>
+      <sheetName val="パラメータ_dimautocon"/>
+      <sheetName val="パラメータ_dimcalprcnt"/>
+      <sheetName val="パラメータ_dimmanualstep"/>
+      <sheetName val="パラメータ_dimmgr"/>
+      <sheetName val="XX-0080"/>
+      <sheetName val="メッセージ定義"/>
+      <sheetName val="XX-0180"/>
+      <sheetName val="lock"/>
+      <sheetName val="level"/>
+      <sheetName val="cominf"/>
+      <sheetName val="disconnect"/>
+      <sheetName val="９ｘ"/>
+      <sheetName val="Ｂｘ"/>
+      <sheetName val="Ｃｘ"/>
+      <sheetName val="Ｅｘ"/>
+      <sheetName val="休日"/>
+      <sheetName val="HMI-004_Screen（old）"/>
+      <sheetName val="ﾊﾟｲﾌﾟ"/>
+      <sheetName val="冷延鋼板"/>
+      <sheetName val="熱延鋼板"/>
+      <sheetName val="他材料費"/>
+      <sheetName val="MOTO"/>
+      <sheetName val="前提書情報"/>
+      <sheetName val="②P071中計　工数パターン1312更新"/>
+      <sheetName val="module"/>
+      <sheetName val="選択肢"/>
+      <sheetName val="vocabulary"/>
+      <sheetName val="メニュー"/>
+      <sheetName val="Calibration"/>
+      <sheetName val="R0-10表紙MIC"/>
+      <sheetName val="CVBS"/>
+      <sheetName val="修正ﾌｧｲﾙ一覧"/>
+      <sheetName val="RGB"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -19450,6 +20305,51 @@
       <sheetData sheetId="93" refreshError="1"/>
       <sheetData sheetId="94" refreshError="1"/>
       <sheetData sheetId="95" refreshError="1"/>
+      <sheetData sheetId="96" refreshError="1"/>
+      <sheetData sheetId="97" refreshError="1"/>
+      <sheetData sheetId="98" refreshError="1"/>
+      <sheetData sheetId="99" refreshError="1"/>
+      <sheetData sheetId="100" refreshError="1"/>
+      <sheetData sheetId="101" refreshError="1"/>
+      <sheetData sheetId="102" refreshError="1"/>
+      <sheetData sheetId="103" refreshError="1"/>
+      <sheetData sheetId="104" refreshError="1"/>
+      <sheetData sheetId="105" refreshError="1"/>
+      <sheetData sheetId="106" refreshError="1"/>
+      <sheetData sheetId="107" refreshError="1"/>
+      <sheetData sheetId="108" refreshError="1"/>
+      <sheetData sheetId="109" refreshError="1"/>
+      <sheetData sheetId="110" refreshError="1"/>
+      <sheetData sheetId="111" refreshError="1"/>
+      <sheetData sheetId="112" refreshError="1"/>
+      <sheetData sheetId="113" refreshError="1"/>
+      <sheetData sheetId="114" refreshError="1"/>
+      <sheetData sheetId="115" refreshError="1"/>
+      <sheetData sheetId="116" refreshError="1"/>
+      <sheetData sheetId="117" refreshError="1"/>
+      <sheetData sheetId="118" refreshError="1"/>
+      <sheetData sheetId="119" refreshError="1"/>
+      <sheetData sheetId="120" refreshError="1"/>
+      <sheetData sheetId="121" refreshError="1"/>
+      <sheetData sheetId="122" refreshError="1"/>
+      <sheetData sheetId="123" refreshError="1"/>
+      <sheetData sheetId="124" refreshError="1"/>
+      <sheetData sheetId="125" refreshError="1"/>
+      <sheetData sheetId="126" refreshError="1"/>
+      <sheetData sheetId="127" refreshError="1"/>
+      <sheetData sheetId="128" refreshError="1"/>
+      <sheetData sheetId="129" refreshError="1"/>
+      <sheetData sheetId="130" refreshError="1"/>
+      <sheetData sheetId="131" refreshError="1"/>
+      <sheetData sheetId="132" refreshError="1"/>
+      <sheetData sheetId="133" refreshError="1"/>
+      <sheetData sheetId="134" refreshError="1"/>
+      <sheetData sheetId="135" refreshError="1"/>
+      <sheetData sheetId="136" refreshError="1"/>
+      <sheetData sheetId="137" refreshError="1"/>
+      <sheetData sheetId="138" refreshError="1"/>
+      <sheetData sheetId="139" refreshError="1"/>
+      <sheetData sheetId="140" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -19746,10 +20646,10 @@
     <tabColor theme="5"/>
   </sheetPr>
   <dimension ref="C1:AM57"/>
-  <sheetFormatPr defaultColWidth="8.125" defaultRowHeight="15.75"/>
+  <sheetFormatPr defaultColWidth="8.08984375" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="52" width="2.125" style="242" customWidth="1"/>
-    <col min="53" max="16384" width="8.125" style="242"/>
+    <col min="1" max="52" width="2.08984375" style="242" customWidth="1"/>
+    <col min="53" max="16384" width="8.08984375" style="242"/>
   </cols>
   <sheetData>
     <row r="1" spans="6:20" ht="13.15" customHeight="1"/>
@@ -19808,31 +20708,31 @@
     </row>
     <row r="34" spans="3:39" ht="13.15" customHeight="1">
       <c r="Y34" s="245" t="s">
-        <v>297</v>
+        <v>314</v>
       </c>
     </row>
     <row r="35" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y35" s="267" t="s">
-        <v>298</v>
-      </c>
-      <c r="Z35" s="268"/>
-      <c r="AA35" s="268"/>
-      <c r="AB35" s="268"/>
-      <c r="AC35" s="269"/>
-      <c r="AD35" s="267" t="s">
-        <v>299</v>
-      </c>
-      <c r="AE35" s="268"/>
-      <c r="AF35" s="268"/>
-      <c r="AG35" s="268"/>
-      <c r="AH35" s="269"/>
-      <c r="AI35" s="267" t="s">
-        <v>300</v>
-      </c>
-      <c r="AJ35" s="268"/>
-      <c r="AK35" s="268"/>
-      <c r="AL35" s="268"/>
-      <c r="AM35" s="269"/>
+      <c r="Y35" s="272" t="s">
+        <v>295</v>
+      </c>
+      <c r="Z35" s="273"/>
+      <c r="AA35" s="273"/>
+      <c r="AB35" s="273"/>
+      <c r="AC35" s="274"/>
+      <c r="AD35" s="272" t="s">
+        <v>296</v>
+      </c>
+      <c r="AE35" s="273"/>
+      <c r="AF35" s="273"/>
+      <c r="AG35" s="273"/>
+      <c r="AH35" s="274"/>
+      <c r="AI35" s="272" t="s">
+        <v>297</v>
+      </c>
+      <c r="AJ35" s="273"/>
+      <c r="AK35" s="273"/>
+      <c r="AL35" s="273"/>
+      <c r="AM35" s="274"/>
     </row>
     <row r="36" spans="3:39" ht="13.15" customHeight="1">
       <c r="D36" s="246"/>
@@ -19878,21 +20778,21 @@
       <c r="Y38" s="251"/>
       <c r="Z38" s="246"/>
       <c r="AA38" s="247" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="AB38" s="246"/>
       <c r="AC38" s="253"/>
       <c r="AD38" s="251"/>
       <c r="AE38" s="246"/>
       <c r="AF38" s="247" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="AG38" s="246"/>
       <c r="AH38" s="253"/>
       <c r="AI38" s="254"/>
       <c r="AJ38" s="246"/>
       <c r="AK38" s="247" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="AL38" s="246"/>
       <c r="AM38" s="253"/>
@@ -19927,31 +20827,31 @@
     <row r="41" spans="3:39" ht="13.15" customHeight="1"/>
     <row r="42" spans="3:39" ht="13.15" customHeight="1">
       <c r="Y42" s="245" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="43" spans="3:39" ht="13.15" customHeight="1">
-      <c r="Y43" s="267" t="s">
-        <v>298</v>
-      </c>
-      <c r="Z43" s="268"/>
-      <c r="AA43" s="268"/>
-      <c r="AB43" s="268"/>
-      <c r="AC43" s="269"/>
-      <c r="AD43" s="267" t="s">
-        <v>299</v>
-      </c>
-      <c r="AE43" s="268"/>
-      <c r="AF43" s="268"/>
-      <c r="AG43" s="268"/>
-      <c r="AH43" s="269"/>
-      <c r="AI43" s="267" t="s">
-        <v>300</v>
-      </c>
-      <c r="AJ43" s="268"/>
-      <c r="AK43" s="268"/>
-      <c r="AL43" s="268"/>
-      <c r="AM43" s="269"/>
+      <c r="Y43" s="272" t="s">
+        <v>295</v>
+      </c>
+      <c r="Z43" s="273"/>
+      <c r="AA43" s="273"/>
+      <c r="AB43" s="273"/>
+      <c r="AC43" s="274"/>
+      <c r="AD43" s="272" t="s">
+        <v>296</v>
+      </c>
+      <c r="AE43" s="273"/>
+      <c r="AF43" s="273"/>
+      <c r="AG43" s="273"/>
+      <c r="AH43" s="274"/>
+      <c r="AI43" s="272" t="s">
+        <v>297</v>
+      </c>
+      <c r="AJ43" s="273"/>
+      <c r="AK43" s="273"/>
+      <c r="AL43" s="273"/>
+      <c r="AM43" s="274"/>
     </row>
     <row r="44" spans="3:39" ht="13.15" customHeight="1">
       <c r="D44" s="246"/>
@@ -19997,21 +20897,21 @@
       <c r="Y46" s="251"/>
       <c r="Z46" s="246"/>
       <c r="AA46" s="247" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="AB46" s="246"/>
       <c r="AC46" s="253"/>
       <c r="AD46" s="246"/>
       <c r="AE46" s="246"/>
       <c r="AF46" s="247" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="AG46" s="246"/>
       <c r="AH46" s="253"/>
       <c r="AI46" s="254"/>
       <c r="AJ46" s="246"/>
       <c r="AK46" s="247" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="AL46" s="246"/>
       <c r="AM46" s="253"/>
@@ -20045,31 +20945,31 @@
     <row r="49" spans="4:39" ht="13.15" customHeight="1"/>
     <row r="50" spans="4:39" ht="13.15" customHeight="1">
       <c r="Y50" s="245" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
     </row>
     <row r="51" spans="4:39" ht="13.15" customHeight="1">
-      <c r="Y51" s="267" t="s">
-        <v>298</v>
-      </c>
-      <c r="Z51" s="268"/>
-      <c r="AA51" s="268"/>
-      <c r="AB51" s="268"/>
-      <c r="AC51" s="269"/>
-      <c r="AD51" s="267" t="s">
-        <v>299</v>
-      </c>
-      <c r="AE51" s="268"/>
-      <c r="AF51" s="268"/>
-      <c r="AG51" s="268"/>
-      <c r="AH51" s="269"/>
-      <c r="AI51" s="267" t="s">
-        <v>300</v>
-      </c>
-      <c r="AJ51" s="268"/>
-      <c r="AK51" s="268"/>
-      <c r="AL51" s="268"/>
-      <c r="AM51" s="269"/>
+      <c r="Y51" s="272" t="s">
+        <v>295</v>
+      </c>
+      <c r="Z51" s="273"/>
+      <c r="AA51" s="273"/>
+      <c r="AB51" s="273"/>
+      <c r="AC51" s="274"/>
+      <c r="AD51" s="272" t="s">
+        <v>296</v>
+      </c>
+      <c r="AE51" s="273"/>
+      <c r="AF51" s="273"/>
+      <c r="AG51" s="273"/>
+      <c r="AH51" s="274"/>
+      <c r="AI51" s="272" t="s">
+        <v>297</v>
+      </c>
+      <c r="AJ51" s="273"/>
+      <c r="AK51" s="273"/>
+      <c r="AL51" s="273"/>
+      <c r="AM51" s="274"/>
     </row>
     <row r="52" spans="4:39" ht="13.15" customHeight="1">
       <c r="D52" s="246"/>
@@ -20115,21 +21015,21 @@
       <c r="Y54" s="251"/>
       <c r="Z54" s="246"/>
       <c r="AA54" s="247" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="AB54" s="246"/>
       <c r="AC54" s="253"/>
       <c r="AD54" s="246"/>
       <c r="AE54" s="246"/>
       <c r="AF54" s="247" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="AG54" s="246"/>
       <c r="AH54" s="253"/>
       <c r="AI54" s="254"/>
       <c r="AJ54" s="246"/>
       <c r="AK54" s="247" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="AL54" s="246"/>
       <c r="AM54" s="253"/>
@@ -20160,7 +21060,7 @@
     </row>
     <row r="57" spans="4:39" ht="13.15" customHeight="1">
       <c r="AK57" s="242" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -20189,14 +21089,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
   <dimension ref="B2:X13"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="1" max="1" width="4.5" customWidth="1"/>
+    <col min="1" max="1" width="4.453125" customWidth="1"/>
     <col min="2" max="2" width="9" style="9" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="69.5" customWidth="1"/>
-    <col min="5" max="6" width="12.75" customWidth="1"/>
-    <col min="7" max="22" width="13.125" hidden="1" customWidth="1"/>
-    <col min="23" max="24" width="13.125" customWidth="1"/>
+    <col min="4" max="4" width="69.453125" customWidth="1"/>
+    <col min="5" max="6" width="12.7265625" customWidth="1"/>
+    <col min="7" max="22" width="13.08984375" hidden="1" customWidth="1"/>
+    <col min="23" max="24" width="13.08984375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="2:24" ht="25.5" customHeight="1">
@@ -20207,18 +21107,18 @@
       <c r="H2" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="I2" s="278" t="s">
+      <c r="I2" s="275" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="278"/>
-      <c r="K2" s="278"/>
-      <c r="L2" s="278"/>
-      <c r="M2" s="278"/>
-      <c r="N2" s="278"/>
-      <c r="O2" s="278"/>
-      <c r="P2" s="278"/>
-      <c r="Q2" s="278"/>
-      <c r="R2" s="278"/>
+      <c r="J2" s="275"/>
+      <c r="K2" s="275"/>
+      <c r="L2" s="275"/>
+      <c r="M2" s="275"/>
+      <c r="N2" s="275"/>
+      <c r="O2" s="275"/>
+      <c r="P2" s="275"/>
+      <c r="Q2" s="275"/>
+      <c r="R2" s="275"/>
     </row>
     <row r="3" spans="2:24" ht="25.5" customHeight="1">
       <c r="C3" s="6"/>
@@ -20231,25 +21131,25 @@
       <c r="H3" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="I3" s="279" t="s">
+      <c r="I3" s="276" t="s">
         <v>193</v>
       </c>
-      <c r="J3" s="280"/>
-      <c r="K3" s="280"/>
-      <c r="L3" s="280"/>
-      <c r="M3" s="280"/>
-      <c r="N3" s="280"/>
-      <c r="O3" s="280"/>
-      <c r="P3" s="280"/>
-      <c r="Q3" s="280"/>
-      <c r="R3" s="280"/>
+      <c r="J3" s="277"/>
+      <c r="K3" s="277"/>
+      <c r="L3" s="277"/>
+      <c r="M3" s="277"/>
+      <c r="N3" s="277"/>
+      <c r="O3" s="277"/>
+      <c r="P3" s="277"/>
+      <c r="Q3" s="277"/>
+      <c r="R3" s="277"/>
     </row>
     <row r="4" spans="2:24" ht="25.5" customHeight="1">
       <c r="C4" s="6"/>
       <c r="D4" s="6"/>
       <c r="E4" s="20" t="str">
         <f>DGET(B8:C14,"Ver.",H4:H5)</f>
-        <v>1.0.1</v>
+        <v>1.0.2</v>
       </c>
       <c r="F4" s="6"/>
       <c r="H4" s="9" t="s">
@@ -20263,45 +21163,45 @@
       <c r="F5" s="6"/>
       <c r="H5" s="11">
         <f>MAX(B9:B14)</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="2:24" ht="13.5" thickBot="1"/>
+    <row r="7" spans="2:24">
+      <c r="C7" s="280" t="s">
+        <v>0</v>
+      </c>
+      <c r="D7" s="281"/>
+      <c r="E7" s="282" t="s">
         <v>2</v>
       </c>
+      <c r="F7" s="282"/>
+      <c r="G7" s="283" t="s">
+        <v>5</v>
+      </c>
+      <c r="H7" s="283"/>
+      <c r="I7" s="283"/>
+      <c r="J7" s="283"/>
+      <c r="K7" s="283"/>
+      <c r="L7" s="283"/>
+      <c r="M7" s="284" t="s">
+        <v>12</v>
+      </c>
+      <c r="N7" s="284"/>
+      <c r="O7" s="284"/>
+      <c r="P7" s="284"/>
+      <c r="Q7" s="284"/>
+      <c r="R7" s="285"/>
+      <c r="S7" s="278" t="s">
+        <v>309</v>
+      </c>
+      <c r="T7" s="278"/>
+      <c r="U7" s="278"/>
+      <c r="V7" s="278"/>
+      <c r="W7" s="278"/>
+      <c r="X7" s="279"/>
     </row>
-    <row r="6" spans="2:24" ht="14.25" thickBot="1"/>
-    <row r="7" spans="2:24">
-      <c r="C7" s="272" t="s">
-        <v>0</v>
-      </c>
-      <c r="D7" s="273"/>
-      <c r="E7" s="274" t="s">
-        <v>2</v>
-      </c>
-      <c r="F7" s="274"/>
-      <c r="G7" s="275" t="s">
-        <v>5</v>
-      </c>
-      <c r="H7" s="275"/>
-      <c r="I7" s="275"/>
-      <c r="J7" s="275"/>
-      <c r="K7" s="275"/>
-      <c r="L7" s="275"/>
-      <c r="M7" s="276" t="s">
-        <v>12</v>
-      </c>
-      <c r="N7" s="276"/>
-      <c r="O7" s="276"/>
-      <c r="P7" s="276"/>
-      <c r="Q7" s="276"/>
-      <c r="R7" s="277"/>
-      <c r="S7" s="270" t="s">
-        <v>312</v>
-      </c>
-      <c r="T7" s="270"/>
-      <c r="U7" s="270"/>
-      <c r="V7" s="270"/>
-      <c r="W7" s="270"/>
-      <c r="X7" s="271"/>
-    </row>
-    <row r="8" spans="2:24" ht="27.75" thickBot="1">
+    <row r="8" spans="2:24" ht="26.5" thickBot="1">
       <c r="B8" s="9" t="s">
         <v>16</v>
       </c>
@@ -20354,7 +21254,7 @@
         <v>11</v>
       </c>
       <c r="S8" s="15" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="T8" s="15" t="s">
         <v>7</v>
@@ -20372,7 +21272,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:24" ht="108.75" thickTop="1">
+    <row r="9" spans="2:24" ht="104.5" thickTop="1">
       <c r="B9" s="9">
         <f>IF(C9=0,0,ROW()-ROW($B$8))</f>
         <v>1</v>
@@ -20381,7 +21281,7 @@
         <v>15</v>
       </c>
       <c r="D9" s="264" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E9" s="265" t="s">
         <v>30</v>
@@ -20412,7 +21312,7 @@
       <c r="O9" s="265"/>
       <c r="P9" s="266"/>
       <c r="Q9" s="265" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="R9" s="266">
         <v>44279</v>
@@ -20436,16 +21336,16 @@
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="2:24" ht="40.5">
+    <row r="10" spans="2:24" ht="39">
       <c r="B10" s="9">
         <f t="shared" ref="B10:B13" si="0">IF(C10=0,0,ROW()-ROW($B$8))</f>
         <v>2</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="D10" s="235" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>30</v>
@@ -20482,21 +21382,29 @@
       <c r="U10" s="1"/>
       <c r="V10" s="260"/>
       <c r="W10" s="1" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="X10" s="236">
         <v>45807</v>
       </c>
     </row>
-    <row r="11" spans="2:24">
+    <row r="11" spans="2:24" ht="91">
       <c r="B11" s="9">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="C11" s="2"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
+        <v>3</v>
+      </c>
+      <c r="C11" s="267" t="s">
+        <v>315</v>
+      </c>
+      <c r="D11" s="268" t="s">
+        <v>318</v>
+      </c>
+      <c r="E11" s="269" t="s">
+        <v>30</v>
+      </c>
+      <c r="F11" s="269" t="s">
+        <v>30</v>
+      </c>
       <c r="G11" s="1"/>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -20513,8 +21421,12 @@
       <c r="T11" s="260"/>
       <c r="U11" s="1"/>
       <c r="V11" s="260"/>
-      <c r="W11" s="1"/>
-      <c r="X11" s="236"/>
+      <c r="W11" s="270" t="s">
+        <v>316</v>
+      </c>
+      <c r="X11" s="271">
+        <v>46008</v>
+      </c>
     </row>
     <row r="12" spans="2:24">
       <c r="B12" s="9">
@@ -20544,7 +21456,7 @@
       <c r="W12" s="1"/>
       <c r="X12" s="236"/>
     </row>
-    <row r="13" spans="2:24" ht="14.25" thickBot="1">
+    <row r="13" spans="2:24" ht="13.5" thickBot="1">
       <c r="B13" s="9">
         <f t="shared" si="0"/>
         <v>0</v>
@@ -20598,11 +21510,11 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet4"/>
   <dimension ref="B2:E39"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="4.625" customWidth="1"/>
-    <col min="3" max="3" width="3.5" customWidth="1"/>
-    <col min="4" max="4" width="17.5" customWidth="1"/>
+    <col min="2" max="2" width="4.6328125" customWidth="1"/>
+    <col min="3" max="3" width="3.453125" customWidth="1"/>
+    <col min="4" max="4" width="17.453125" customWidth="1"/>
     <col min="5" max="5" width="106" customWidth="1"/>
   </cols>
   <sheetData>
@@ -20616,13 +21528,13 @@
         <v>136</v>
       </c>
     </row>
-    <row r="6" spans="2:5" ht="14.25" thickBot="1">
+    <row r="6" spans="2:5" ht="13.5" thickBot="1">
       <c r="B6" s="142" t="s">
         <v>127</v>
       </c>
       <c r="C6" s="142"/>
     </row>
-    <row r="7" spans="2:5" ht="14.25" thickBot="1">
+    <row r="7" spans="2:5" ht="13.5" thickBot="1">
       <c r="C7" s="71" t="s">
         <v>129</v>
       </c>
@@ -20642,7 +21554,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="9" spans="2:5" ht="27">
+    <row r="9" spans="2:5" ht="26">
       <c r="C9" s="152">
         <v>1</v>
       </c>
@@ -20653,7 +21565,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="10" spans="2:5" ht="14.25" thickBot="1">
+    <row r="10" spans="2:5" ht="13.5" thickBot="1">
       <c r="C10" s="150"/>
       <c r="D10" s="82"/>
       <c r="E10" s="5"/>
@@ -20661,14 +21573,14 @@
     <row r="11" spans="2:5">
       <c r="C11" s="148"/>
     </row>
-    <row r="12" spans="2:5" ht="14.25" thickBot="1">
+    <row r="12" spans="2:5" ht="13.5" thickBot="1">
       <c r="B12" s="143" t="s">
         <v>128</v>
       </c>
       <c r="C12" s="78"/>
       <c r="D12" s="78"/>
     </row>
-    <row r="13" spans="2:5" ht="14.25" thickBot="1">
+    <row r="13" spans="2:5" ht="13.5" thickBot="1">
       <c r="B13" s="144"/>
       <c r="C13" s="149" t="s">
         <v>129</v>
@@ -20680,7 +21592,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="14" spans="2:5" ht="14.25" thickTop="1">
+    <row r="14" spans="2:5" ht="13.5" thickTop="1">
       <c r="C14" s="146">
         <v>0</v>
       </c>
@@ -20757,17 +21669,17 @@
         <v>164</v>
       </c>
     </row>
-    <row r="21" spans="2:5" ht="14.25" thickBot="1">
+    <row r="21" spans="2:5" ht="13.5" thickBot="1">
       <c r="C21" s="150"/>
       <c r="D21" s="82"/>
       <c r="E21" s="5"/>
     </row>
-    <row r="24" spans="2:5" ht="14.25" thickBot="1">
+    <row r="24" spans="2:5" ht="13.5" thickBot="1">
       <c r="B24" s="142" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="25" spans="2:5" ht="14.25" thickBot="1">
+    <row r="25" spans="2:5" ht="13.5" thickBot="1">
       <c r="C25" s="149" t="s">
         <v>129</v>
       </c>
@@ -20854,26 +21766,26 @@
       <c r="D33" s="81"/>
       <c r="E33" s="67"/>
     </row>
-    <row r="34" spans="2:5" ht="14.25" thickBot="1">
+    <row r="34" spans="2:5" ht="13.5" thickBot="1">
       <c r="C34" s="150"/>
       <c r="D34" s="82"/>
       <c r="E34" s="5"/>
     </row>
-    <row r="37" spans="2:5" ht="14.25" thickBot="1">
+    <row r="37" spans="2:5" ht="13.5" thickBot="1">
       <c r="B37" s="142" t="s">
         <v>160</v>
       </c>
     </row>
     <row r="38" spans="2:5">
-      <c r="C38" s="281"/>
-      <c r="D38" s="282"/>
+      <c r="C38" s="286"/>
+      <c r="D38" s="287"/>
       <c r="E38" s="107" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="39" spans="2:5" ht="14.25" thickBot="1">
-      <c r="C39" s="283"/>
-      <c r="D39" s="284"/>
+    <row r="39" spans="2:5" ht="13.5" thickBot="1">
+      <c r="C39" s="288"/>
+      <c r="D39" s="289"/>
       <c r="E39" s="5" t="s">
         <v>117</v>
       </c>
@@ -20902,131 +21814,131 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:N37"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="26.75" customWidth="1"/>
-    <col min="9" max="9" width="20.875" hidden="1" customWidth="1"/>
+    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="26.7265625" customWidth="1"/>
+    <col min="9" max="9" width="20.90625" hidden="1" customWidth="1"/>
     <col min="10" max="14" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:14" ht="14.25" thickBot="1"/>
+    <row r="1" spans="2:14" ht="13.5" thickBot="1"/>
     <row r="2" spans="2:14">
-      <c r="B2" s="285" t="s">
+      <c r="B2" s="290" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="286"/>
-      <c r="D2" s="291" t="s">
-        <v>295</v>
-      </c>
-      <c r="E2" s="292"/>
-      <c r="F2" s="292"/>
-      <c r="G2" s="292"/>
-      <c r="H2" s="293"/>
+      <c r="C2" s="291"/>
+      <c r="D2" s="296" t="s">
+        <v>293</v>
+      </c>
+      <c r="E2" s="297"/>
+      <c r="F2" s="297"/>
+      <c r="G2" s="297"/>
+      <c r="H2" s="298"/>
     </row>
     <row r="3" spans="2:14">
-      <c r="B3" s="287" t="s">
+      <c r="B3" s="292" t="s">
         <v>114</v>
       </c>
-      <c r="C3" s="288"/>
-      <c r="D3" s="294" t="s">
-        <v>293</v>
-      </c>
-      <c r="E3" s="295"/>
-      <c r="F3" s="295"/>
-      <c r="G3" s="295"/>
-      <c r="H3" s="296"/>
+      <c r="C3" s="293"/>
+      <c r="D3" s="299" t="s">
+        <v>291</v>
+      </c>
+      <c r="E3" s="300"/>
+      <c r="F3" s="300"/>
+      <c r="G3" s="300"/>
+      <c r="H3" s="301"/>
     </row>
-    <row r="4" spans="2:14" ht="14.25" thickBot="1">
-      <c r="B4" s="289" t="s">
+    <row r="4" spans="2:14" ht="13.5" thickBot="1">
+      <c r="B4" s="294" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="290"/>
-      <c r="D4" s="297" t="str">
+      <c r="C4" s="295"/>
+      <c r="D4" s="302" t="str">
         <f ca="1">表紙!D3&amp;".c"</f>
         <v>alert_C_MCBW-CSTD-0-01-B-C0.c</v>
       </c>
-      <c r="E4" s="298"/>
-      <c r="F4" s="298"/>
-      <c r="G4" s="298"/>
-      <c r="H4" s="299"/>
+      <c r="E4" s="303"/>
+      <c r="F4" s="303"/>
+      <c r="G4" s="303"/>
+      <c r="H4" s="304"/>
     </row>
-    <row r="5" spans="2:14" ht="14.25" thickBot="1">
+    <row r="5" spans="2:14" ht="13.5" thickBot="1">
       <c r="D5" t="str">
         <f ca="1">IF(LEN(表紙!D3&amp;".c") = LENB(表紙!D3&amp;".c"),"※モジュール名 全角チェックOK","※モジュール名 全角チェックNG：ファイル名に全角文字が使用されています！")</f>
         <v>※モジュール名 全角チェックOK</v>
       </c>
     </row>
     <row r="6" spans="2:14">
-      <c r="B6" s="285" t="s">
+      <c r="B6" s="290" t="s">
         <v>35</v>
       </c>
-      <c r="C6" s="286"/>
-      <c r="D6" s="300" t="str">
+      <c r="C6" s="291"/>
+      <c r="D6" s="305" t="str">
         <f ca="1">MID(D4, LEN("alert_") + 1, FIND("-",D4,1) - LEN("alert_") - 1)</f>
         <v>C_MCBW</v>
       </c>
-      <c r="E6" s="301"/>
-      <c r="F6" s="301"/>
-      <c r="G6" s="301"/>
-      <c r="H6" s="302"/>
+      <c r="E6" s="306"/>
+      <c r="F6" s="306"/>
+      <c r="G6" s="306"/>
+      <c r="H6" s="307"/>
     </row>
     <row r="7" spans="2:14">
-      <c r="B7" s="287" t="s">
+      <c r="B7" s="292" t="s">
         <v>36</v>
       </c>
-      <c r="C7" s="288"/>
-      <c r="D7" s="303">
+      <c r="C7" s="293"/>
+      <c r="D7" s="308">
         <f>COUNTA($D$13:$D$37)</f>
         <v>1</v>
       </c>
-      <c r="E7" s="304"/>
-      <c r="F7" s="304"/>
-      <c r="G7" s="304"/>
-      <c r="H7" s="305"/>
+      <c r="E7" s="309"/>
+      <c r="F7" s="309"/>
+      <c r="G7" s="309"/>
+      <c r="H7" s="310"/>
     </row>
     <row r="8" spans="2:14">
-      <c r="B8" s="287" t="s">
+      <c r="B8" s="292" t="s">
         <v>93</v>
       </c>
-      <c r="C8" s="288"/>
-      <c r="D8" s="303" t="str">
+      <c r="C8" s="293"/>
+      <c r="D8" s="308" t="str">
         <f ca="1">"st_gp_ALERT_"&amp;UPPER(D6)&amp;"_MTRX"</f>
         <v>st_gp_ALERT_C_MCBW_MTRX</v>
       </c>
-      <c r="E8" s="304"/>
-      <c r="F8" s="304"/>
-      <c r="G8" s="304"/>
-      <c r="H8" s="305"/>
+      <c r="E8" s="309"/>
+      <c r="F8" s="309"/>
+      <c r="G8" s="309"/>
+      <c r="H8" s="310"/>
     </row>
     <row r="9" spans="2:14">
-      <c r="B9" s="287" t="s">
+      <c r="B9" s="292" t="s">
         <v>37</v>
       </c>
-      <c r="C9" s="288"/>
-      <c r="D9" s="306" t="s">
-        <v>277</v>
-      </c>
-      <c r="E9" s="307"/>
-      <c r="F9" s="307"/>
-      <c r="G9" s="307"/>
-      <c r="H9" s="308"/>
+      <c r="C9" s="293"/>
+      <c r="D9" s="311" t="s">
+        <v>275</v>
+      </c>
+      <c r="E9" s="312"/>
+      <c r="F9" s="312"/>
+      <c r="G9" s="312"/>
+      <c r="H9" s="313"/>
     </row>
-    <row r="10" spans="2:14" ht="14.25" thickBot="1">
-      <c r="B10" s="289" t="s">
+    <row r="10" spans="2:14" ht="13.5" thickBot="1">
+      <c r="B10" s="294" t="s">
         <v>43</v>
       </c>
-      <c r="C10" s="290"/>
-      <c r="D10" s="309"/>
-      <c r="E10" s="310"/>
-      <c r="F10" s="310"/>
-      <c r="G10" s="310"/>
-      <c r="H10" s="311"/>
+      <c r="C10" s="295"/>
+      <c r="D10" s="314"/>
+      <c r="E10" s="315"/>
+      <c r="F10" s="315"/>
+      <c r="G10" s="315"/>
+      <c r="H10" s="316"/>
     </row>
-    <row r="11" spans="2:14" ht="14.25" thickBot="1"/>
-    <row r="12" spans="2:14" ht="14.25" thickBot="1">
+    <row r="11" spans="2:14" ht="13.5" thickBot="1"/>
+    <row r="12" spans="2:14" ht="13.5" thickBot="1">
       <c r="B12" s="133" t="s">
         <v>33</v>
       </c>
@@ -21061,7 +21973,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="2:14" ht="14.25" thickTop="1">
+    <row r="13" spans="2:14" ht="13.5" thickTop="1">
       <c r="B13" s="100">
         <v>1</v>
       </c>
@@ -21072,15 +21984,15 @@
         <v>47</v>
       </c>
       <c r="E13" s="106" t="s">
-        <v>203</v>
+        <v>317</v>
       </c>
       <c r="F13" s="44" t="str">
         <f t="shared" ref="F13:F37" ca="1" si="0">IF($D13&lt;&gt;"","u4_s_Alert"&amp;UPPER(LEFT($D$6,1))&amp;LOWER(MID($D$6,2,100))&amp;IF($D$7=1,"",N13)&amp;"Srcchk","")</f>
         <v>u4_s_AlertC_mcbwSrcchk</v>
       </c>
       <c r="G13" s="44" t="str">
-        <f t="shared" ref="G13:G37" ca="1" si="1">IF($D13&lt;&gt;"",IF($E13="○","vd_s_Alert"&amp;UPPER(LEFT($D$6,1))&amp;LOWER(MID($D$6,2,100))&amp;IF($D$7=1,"",N13)&amp;"RwTx","NULL"),"")</f>
-        <v>vd_s_AlertC_mcbwRwTx</v>
+        <f t="shared" ref="G13:G37" si="1">IF($D13&lt;&gt;"",IF($E13="○","vd_s_Alert"&amp;UPPER(LEFT($D$6,1))&amp;LOWER(MID($D$6,2,100))&amp;IF($D$7=1,"",N13)&amp;"RwTx","NULL"),"")</f>
+        <v>NULL</v>
       </c>
       <c r="H13" s="104" t="str">
         <f ca="1">IF($D13&lt;&gt;"","ALERT_CH_"&amp;UPPER($D$6)&amp;IF($D$7=1,"","_"&amp;UPPER($C13)),"")</f>
@@ -21914,7 +22826,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="2:14" ht="14.25" thickBot="1">
+    <row r="37" spans="2:14" ht="13.5" thickBot="1">
       <c r="B37" s="91">
         <v>25</v>
       </c>
@@ -22013,21 +22925,21 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B2:R59"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="3.75" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="19.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="3.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.08984375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="13" customWidth="1"/>
-    <col min="5" max="5" width="36.5" customWidth="1"/>
-    <col min="6" max="6" width="52.75" customWidth="1"/>
-    <col min="7" max="7" width="7.125" bestFit="1" customWidth="1"/>
-    <col min="8" max="15" width="3.875" customWidth="1"/>
-    <col min="16" max="16" width="9.875" customWidth="1"/>
-    <col min="17" max="17" width="44.625" customWidth="1"/>
-    <col min="18" max="18" width="73.625" customWidth="1"/>
+    <col min="5" max="5" width="36.453125" customWidth="1"/>
+    <col min="6" max="6" width="52.7265625" customWidth="1"/>
+    <col min="7" max="7" width="7.08984375" bestFit="1" customWidth="1"/>
+    <col min="8" max="15" width="3.90625" customWidth="1"/>
+    <col min="16" max="16" width="9.90625" customWidth="1"/>
+    <col min="17" max="17" width="44.6328125" customWidth="1"/>
+    <col min="18" max="18" width="73.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:18" ht="14.25" thickBot="1">
+    <row r="2" spans="2:18" ht="13.5" thickBot="1">
       <c r="B2" t="s">
         <v>185</v>
       </c>
@@ -22035,7 +22947,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="3" spans="2:18" ht="14.25" thickBot="1">
+    <row r="3" spans="2:18" ht="13.5" thickBot="1">
       <c r="B3" s="133" t="s">
         <v>33</v>
       </c>
@@ -22073,7 +22985,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="4" spans="2:18" ht="14.25" hidden="1" thickTop="1">
+    <row r="4" spans="2:18" ht="13.5" hidden="1" thickTop="1">
       <c r="B4" s="164">
         <v>0</v>
       </c>
@@ -22101,7 +23013,7 @@
       </c>
       <c r="R4" s="132"/>
     </row>
-    <row r="5" spans="2:18" ht="14.25" thickTop="1">
+    <row r="5" spans="2:18" ht="13.5" thickTop="1">
       <c r="B5" s="167">
         <v>1</v>
       </c>
@@ -22629,7 +23541,7 @@
       <c r="Q28" s="137"/>
       <c r="R28" s="110"/>
     </row>
-    <row r="29" spans="2:18" ht="14.25" thickBot="1">
+    <row r="29" spans="2:18" ht="13.5" thickBot="1">
       <c r="B29" s="168">
         <v>25</v>
       </c>
@@ -22651,7 +23563,7 @@
       <c r="Q29" s="135"/>
       <c r="R29" s="112"/>
     </row>
-    <row r="32" spans="2:18" ht="14.25" thickBot="1">
+    <row r="32" spans="2:18" ht="13.5" thickBot="1">
       <c r="B32" t="s">
         <v>186</v>
       </c>
@@ -22659,7 +23571,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="33" spans="2:18" ht="14.25" thickBot="1">
+    <row r="33" spans="2:18" ht="13.5" thickBot="1">
       <c r="B33" s="133" t="s">
         <v>33</v>
       </c>
@@ -22691,7 +23603,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="34" spans="2:18" ht="14.25" hidden="1" thickTop="1">
+    <row r="34" spans="2:18" ht="13.5" hidden="1" thickTop="1">
       <c r="B34" s="164">
         <v>0</v>
       </c>
@@ -22717,7 +23629,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="35" spans="2:18" ht="14.25" thickTop="1">
+    <row r="35" spans="2:18" ht="13.5" thickTop="1">
       <c r="B35" s="167">
         <v>1</v>
       </c>
@@ -23245,7 +24157,7 @@
       <c r="Q58" s="137"/>
       <c r="R58" s="169"/>
     </row>
-    <row r="59" spans="2:18" ht="14.25" thickBot="1">
+    <row r="59" spans="2:18" ht="13.5" thickBot="1">
       <c r="B59" s="168">
         <v>25</v>
       </c>
@@ -23296,29 +24208,29 @@
     <tabColor rgb="FFCCFFCC"/>
   </sheetPr>
   <dimension ref="B1:U103"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="28.375" customWidth="1"/>
-    <col min="3" max="3" width="15.875" customWidth="1"/>
-    <col min="5" max="5" width="12.375" customWidth="1"/>
-    <col min="6" max="6" width="19.75" customWidth="1"/>
-    <col min="7" max="7" width="12.375" customWidth="1"/>
+    <col min="2" max="2" width="28.36328125" customWidth="1"/>
+    <col min="3" max="3" width="15.90625" customWidth="1"/>
+    <col min="5" max="5" width="12.36328125" customWidth="1"/>
+    <col min="6" max="6" width="19.7265625" customWidth="1"/>
+    <col min="7" max="7" width="12.36328125" customWidth="1"/>
     <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="9" width="12.375" customWidth="1"/>
-    <col min="10" max="10" width="33.5" customWidth="1"/>
-    <col min="11" max="11" width="12.375" customWidth="1"/>
-    <col min="12" max="12" width="16.125" customWidth="1"/>
-    <col min="14" max="14" width="30.125" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="57.125" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="12.36328125" customWidth="1"/>
+    <col min="10" max="10" width="33.453125" customWidth="1"/>
+    <col min="11" max="11" width="12.36328125" customWidth="1"/>
+    <col min="12" max="12" width="16.08984375" customWidth="1"/>
+    <col min="14" max="14" width="30.08984375" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="57.08984375" hidden="1" customWidth="1"/>
     <col min="21" max="21" width="13" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:21" ht="14.25" thickBot="1">
+    <row r="1" spans="2:21" ht="13.5" thickBot="1">
       <c r="C1" s="84" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="2" spans="2:21" ht="14.25" thickBot="1">
+    <row r="2" spans="2:21" ht="13.5" thickBot="1">
       <c r="B2" s="92" t="s">
         <v>57</v>
       </c>
@@ -23362,7 +24274,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="3" spans="2:21" ht="15" hidden="1" thickTop="1" thickBot="1">
+    <row r="3" spans="2:21" ht="14" hidden="1" thickTop="1" thickBot="1">
       <c r="B3" s="22"/>
       <c r="C3" s="43" t="s">
         <v>106</v>
@@ -23383,12 +24295,12 @@
         <v>96</v>
       </c>
     </row>
-    <row r="4" spans="2:21" ht="14.25" thickTop="1">
+    <row r="4" spans="2:21" ht="13.5" thickTop="1">
       <c r="B4" s="203" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C4" s="193" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="D4" s="204">
         <v>0</v>
@@ -23397,25 +24309,25 @@
         <v>124</v>
       </c>
       <c r="F4" s="227" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G4" s="226" t="s">
         <v>124</v>
       </c>
       <c r="H4" s="227" t="s">
+        <v>243</v>
+      </c>
+      <c r="I4" s="226" t="s">
         <v>244</v>
       </c>
-      <c r="I4" s="226" t="s">
-        <v>245</v>
-      </c>
       <c r="J4" s="227" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="K4" s="226" t="s">
         <v>124</v>
       </c>
       <c r="L4" s="227" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="M4" s="44">
         <f ca="1">LEN(N4)</f>
@@ -23435,7 +24347,7 @@
     </row>
     <row r="5" spans="2:21">
       <c r="B5" s="203" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="C5" s="102" t="s">
         <v>199</v>
@@ -23447,25 +24359,25 @@
         <v>124</v>
       </c>
       <c r="F5" s="195" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G5" s="203" t="s">
         <v>124</v>
       </c>
       <c r="H5" s="195" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="I5" s="203" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="J5" s="227" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="K5" s="203" t="s">
         <v>124</v>
       </c>
       <c r="L5" s="195" t="s">
-        <v>248</v>
+        <v>30</v>
       </c>
       <c r="M5" s="39">
         <f t="shared" ref="M5:M68" ca="1" si="1">LEN(N5)</f>
@@ -23673,7 +24585,7 @@
       </c>
       <c r="U12" s="28"/>
     </row>
-    <row r="13" spans="2:21" ht="14.25" thickBot="1">
+    <row r="13" spans="2:21" ht="13.5" thickBot="1">
       <c r="B13" s="22"/>
       <c r="C13" s="21"/>
       <c r="D13" s="109"/>
@@ -25924,7 +26836,7 @@
         <v>#N/A</v>
       </c>
     </row>
-    <row r="103" spans="2:15" ht="14.25" thickBot="1">
+    <row r="103" spans="2:15" ht="13.5" thickBot="1">
       <c r="B103" s="45"/>
       <c r="C103" s="46"/>
       <c r="D103" s="111"/>
@@ -25997,18 +26909,18 @@
     <tabColor rgb="FFCCECFF"/>
   </sheetPr>
   <dimension ref="A1:AW199"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
-    <col min="2" max="2" width="16.75" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="3" bestFit="1" customWidth="1"/>
     <col min="4" max="35" width="3" customWidth="1"/>
-    <col min="36" max="36" width="36.375" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="4.125" customWidth="1"/>
+    <col min="36" max="36" width="36.36328125" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="4.08984375" customWidth="1"/>
     <col min="38" max="42" width="9" hidden="1" customWidth="1"/>
-    <col min="43" max="43" width="20.625" hidden="1" customWidth="1"/>
-    <col min="44" max="47" width="41.125" customWidth="1"/>
-    <col min="48" max="48" width="23.625" customWidth="1"/>
+    <col min="43" max="43" width="20.6328125" hidden="1" customWidth="1"/>
+    <col min="44" max="47" width="41.08984375" customWidth="1"/>
+    <col min="48" max="48" width="23.6328125" customWidth="1"/>
     <col min="49" max="49" width="29" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -26024,7 +26936,7 @@
       <c r="B2" s="119" t="s">
         <v>121</v>
       </c>
-      <c r="C2" s="312" t="s">
+      <c r="C2" s="317" t="s">
         <v>83</v>
       </c>
       <c r="D2" s="50">
@@ -26123,7 +27035,7 @@
       <c r="AI2" s="50">
         <v>0</v>
       </c>
-      <c r="AJ2" s="314" t="s">
+      <c r="AJ2" s="319" t="s">
         <v>153</v>
       </c>
     </row>
@@ -26132,7 +27044,7 @@
         <f>IF(OR(IF(COUNTIF(D6:AC69,"0")&lt;&gt;0,TRUE,FALSE),IF(COUNTIF(D6:AC69,"1")&lt;&gt;0,TRUE,FALSE)),"Search Table","Index Table")</f>
         <v>Index Table</v>
       </c>
-      <c r="C3" s="313"/>
+      <c r="C3" s="318"/>
       <c r="D3" s="121" t="s">
         <v>60</v>
       </c>
@@ -26215,26 +27127,26 @@
         <v>65</v>
       </c>
       <c r="AE3" s="185" t="s">
-        <v>283</v>
-      </c>
-      <c r="AF3" s="320" t="s">
-        <v>250</v>
-      </c>
-      <c r="AG3" s="321"/>
-      <c r="AH3" s="320" t="s">
-        <v>282</v>
-      </c>
-      <c r="AI3" s="321"/>
-      <c r="AJ3" s="315"/>
+        <v>281</v>
+      </c>
+      <c r="AF3" s="325" t="s">
+        <v>248</v>
+      </c>
+      <c r="AG3" s="326"/>
+      <c r="AH3" s="325" t="s">
+        <v>280</v>
+      </c>
+      <c r="AI3" s="326"/>
+      <c r="AJ3" s="320"/>
       <c r="AR3" s="85" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="4" spans="1:49" ht="14.25" thickBot="1">
-      <c r="A4" s="316" t="s">
+    <row r="4" spans="1:49" ht="13.5" thickBot="1">
+      <c r="A4" s="321" t="s">
         <v>62</v>
       </c>
-      <c r="B4" s="317"/>
+      <c r="B4" s="322"/>
       <c r="C4" s="130"/>
       <c r="D4" s="130"/>
       <c r="E4" s="130"/>
@@ -26278,9 +27190,9 @@
       <c r="AV4" s="74"/>
       <c r="AW4" s="75"/>
     </row>
-    <row r="5" spans="1:49" ht="14.25" thickBot="1">
-      <c r="A5" s="318"/>
-      <c r="B5" s="319"/>
+    <row r="5" spans="1:49" ht="13.5" thickBot="1">
+      <c r="A5" s="323"/>
+      <c r="B5" s="324"/>
       <c r="C5" s="131"/>
       <c r="D5" s="131"/>
       <c r="E5" s="131"/>
@@ -26728,7 +27640,7 @@
       </c>
       <c r="AU8" s="55" t="str">
         <f ca="1">IF($AW$15&lt;&gt;"NULL","        &amp;"&amp;$AW$15&amp;","&amp;REPT(" ",69-LEN($AW$15))&amp;"/* fp_vd_XDST                                         */","        vdp_PTR_NA,                                                            /* fp_vd_XDST                                         */")</f>
-        <v xml:space="preserve">        &amp;vd_s_AlertC_mcbwRwTx,                                                 /* fp_vd_XDST                                         */</v>
+        <v xml:space="preserve">        vdp_PTR_NA,                                                            /* fp_vd_XDST                                         */</v>
       </c>
       <c r="AV8" s="41" t="s">
         <v>71</v>
@@ -26841,7 +27753,7 @@
         <v>1</v>
       </c>
       <c r="AJ9" s="198" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="AL9" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -27660,7 +28572,7 @@
       </c>
       <c r="AW15" s="60" t="str">
         <f ca="1">IF(AW6&lt;&gt;AW17,VLOOKUP(AW6,Matrix!$C$13:$G$37,5,FALSE),Matrix!G13)</f>
-        <v>vd_s_AlertC_mcbwRwTx</v>
+        <v>NULL</v>
       </c>
     </row>
     <row r="16" spans="1:49">
@@ -27795,7 +28707,7 @@
         <v>ALERT_VOM_IGN_ON</v>
       </c>
     </row>
-    <row r="17" spans="2:49" ht="14.25" thickBot="1">
+    <row r="17" spans="2:49" ht="13.5" thickBot="1">
       <c r="B17" s="127"/>
       <c r="C17" s="39">
         <f t="shared" si="2"/>
@@ -27898,7 +28810,7 @@
         <v>1</v>
       </c>
       <c r="AJ17" s="198" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AL17" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -28884,7 +29796,7 @@
         <v>1</v>
       </c>
       <c r="AJ25" s="198" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AL25" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -29860,7 +30772,7 @@
         <v>1</v>
       </c>
       <c r="AJ33" s="198" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="AL33" t="str">
         <f t="shared" ca="1" si="0"/>
@@ -34207,7 +35119,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:46" ht="14.25" thickBot="1">
+    <row r="70" spans="1:46" ht="13.5" thickBot="1">
       <c r="A70" s="48" t="s">
         <v>63</v>
       </c>
@@ -54838,22 +55750,22 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <sheetPr codeName="Sheet5"/>
   <dimension ref="B2:AT90"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="48.625" customWidth="1"/>
-    <col min="3" max="10" width="3.375" customWidth="1"/>
-    <col min="11" max="11" width="20.875" customWidth="1"/>
+    <col min="2" max="2" width="48.6328125" customWidth="1"/>
+    <col min="3" max="10" width="3.36328125" customWidth="1"/>
+    <col min="11" max="11" width="20.90625" customWidth="1"/>
     <col min="12" max="12" width="19" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="19.875" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="19.90625" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="21" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="8.125" customWidth="1"/>
-    <col min="17" max="17" width="8.25" customWidth="1"/>
-    <col min="18" max="18" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="8.08984375" customWidth="1"/>
+    <col min="17" max="17" width="8.26953125" customWidth="1"/>
+    <col min="18" max="18" width="11.90625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:46" ht="15" thickBot="1">
+    <row r="2" spans="2:46" ht="14.5" thickBot="1">
       <c r="B2" s="23" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="V2" s="184" t="s">
         <v>200</v>
@@ -54883,20 +55795,20 @@
       <c r="AS2" s="184"/>
       <c r="AT2" s="184"/>
     </row>
-    <row r="3" spans="2:46" ht="15" thickBot="1">
+    <row r="3" spans="2:46" ht="14.5" thickBot="1">
       <c r="B3" s="89" t="s">
         <v>121</v>
       </c>
-      <c r="C3" s="326" t="s">
-        <v>205</v>
-      </c>
-      <c r="D3" s="327"/>
-      <c r="E3" s="327"/>
-      <c r="F3" s="327"/>
-      <c r="G3" s="327"/>
-      <c r="H3" s="327"/>
-      <c r="I3" s="327"/>
-      <c r="J3" s="328"/>
+      <c r="C3" s="331" t="s">
+        <v>204</v>
+      </c>
+      <c r="D3" s="332"/>
+      <c r="E3" s="332"/>
+      <c r="F3" s="332"/>
+      <c r="G3" s="332"/>
+      <c r="H3" s="332"/>
+      <c r="I3" s="332"/>
+      <c r="J3" s="333"/>
       <c r="K3" s="215"/>
       <c r="L3" s="160"/>
       <c r="M3" s="160"/>
@@ -54909,7 +55821,7 @@
     <row r="4" spans="2:46">
       <c r="B4" s="62"/>
       <c r="C4" s="31" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="D4" s="31"/>
       <c r="E4" s="31"/>
@@ -54935,23 +55847,23 @@
       <c r="B5" s="63" t="s">
         <v>22</v>
       </c>
-      <c r="C5" s="322" t="s">
+      <c r="C5" s="327" t="s">
+        <v>207</v>
+      </c>
+      <c r="D5" s="328"/>
+      <c r="E5" s="328"/>
+      <c r="F5" s="328"/>
+      <c r="G5" s="328"/>
+      <c r="H5" s="328"/>
+      <c r="I5" s="328"/>
+      <c r="J5" s="329"/>
+      <c r="K5" s="216" t="s">
         <v>208</v>
-      </c>
-      <c r="D5" s="323"/>
-      <c r="E5" s="323"/>
-      <c r="F5" s="323"/>
-      <c r="G5" s="323"/>
-      <c r="H5" s="323"/>
-      <c r="I5" s="323"/>
-      <c r="J5" s="324"/>
-      <c r="K5" s="216" t="s">
-        <v>209</v>
       </c>
       <c r="L5" s="216"/>
       <c r="M5" s="66"/>
       <c r="N5" s="28" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="O5" s="69" t="s">
         <v>23</v>
@@ -54966,33 +55878,33 @@
         <v>26</v>
       </c>
     </row>
-    <row r="6" spans="2:46" ht="27">
+    <row r="6" spans="2:46" ht="26">
       <c r="B6" s="63" t="s">
         <v>32</v>
       </c>
       <c r="C6" s="155" t="s">
+        <v>210</v>
+      </c>
+      <c r="D6" s="155" t="s">
+        <v>210</v>
+      </c>
+      <c r="E6" s="155" t="s">
         <v>211</v>
       </c>
-      <c r="D6" s="155" t="s">
+      <c r="F6" s="155" t="s">
+        <v>209</v>
+      </c>
+      <c r="G6" s="155" t="s">
+        <v>209</v>
+      </c>
+      <c r="H6" s="155" t="s">
         <v>211</v>
       </c>
-      <c r="E6" s="155" t="s">
+      <c r="I6" s="155" t="s">
         <v>212</v>
       </c>
-      <c r="F6" s="155" t="s">
-        <v>210</v>
-      </c>
-      <c r="G6" s="155" t="s">
-        <v>210</v>
-      </c>
-      <c r="H6" s="155" t="s">
-        <v>212</v>
-      </c>
-      <c r="I6" s="155" t="s">
+      <c r="J6" s="155" t="s">
         <v>213</v>
-      </c>
-      <c r="J6" s="155" t="s">
-        <v>214</v>
       </c>
       <c r="K6" s="25" t="s">
         <v>195</v>
@@ -55010,172 +55922,172 @@
       <c r="P6" s="218"/>
       <c r="Q6" s="70"/>
       <c r="R6" s="83" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
     </row>
-    <row r="7" spans="2:46" ht="27">
+    <row r="7" spans="2:46" ht="26">
       <c r="B7" s="64" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="325" t="s">
+      <c r="C7" s="330" t="s">
+        <v>215</v>
+      </c>
+      <c r="D7" s="328"/>
+      <c r="E7" s="328"/>
+      <c r="F7" s="328"/>
+      <c r="G7" s="328"/>
+      <c r="H7" s="328"/>
+      <c r="I7" s="328"/>
+      <c r="J7" s="329"/>
+      <c r="K7" s="25" t="s">
         <v>216</v>
       </c>
-      <c r="D7" s="323"/>
-      <c r="E7" s="323"/>
-      <c r="F7" s="323"/>
-      <c r="G7" s="323"/>
-      <c r="H7" s="323"/>
-      <c r="I7" s="323"/>
-      <c r="J7" s="324"/>
-      <c r="K7" s="25" t="s">
-        <v>217</v>
-      </c>
       <c r="L7" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="M7" s="25" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="N7" s="29"/>
       <c r="O7" s="217"/>
       <c r="P7" s="218"/>
       <c r="Q7" s="70"/>
       <c r="R7" s="67" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
     </row>
-    <row r="8" spans="2:46" ht="136.5">
+    <row r="8" spans="2:46" ht="131">
       <c r="B8" s="63" t="s">
         <v>28</v>
       </c>
       <c r="C8" s="156" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D8" s="156" t="s">
         <v>61</v>
       </c>
       <c r="E8" s="156" t="s">
+        <v>218</v>
+      </c>
+      <c r="F8" s="156" t="s">
         <v>219</v>
       </c>
-      <c r="F8" s="156" t="s">
+      <c r="G8" s="156" t="s">
         <v>220</v>
       </c>
-      <c r="G8" s="156" t="s">
+      <c r="H8" s="156" t="s">
         <v>221</v>
       </c>
-      <c r="H8" s="156" t="s">
+      <c r="I8" s="156" t="s">
         <v>222</v>
       </c>
-      <c r="I8" s="156" t="s">
+      <c r="J8" s="156" t="s">
         <v>223</v>
       </c>
-      <c r="J8" s="156" t="s">
+      <c r="K8" s="25" t="s">
+        <v>281</v>
+      </c>
+      <c r="L8" s="1" t="s">
         <v>224</v>
       </c>
-      <c r="K8" s="25" t="s">
-        <v>283</v>
-      </c>
-      <c r="L8" s="1" t="s">
+      <c r="M8" s="25" t="s">
+        <v>280</v>
+      </c>
+      <c r="N8" s="28" t="s">
         <v>225</v>
-      </c>
-      <c r="M8" s="25" t="s">
-        <v>282</v>
-      </c>
-      <c r="N8" s="28" t="s">
-        <v>226</v>
       </c>
       <c r="O8" s="217"/>
       <c r="P8" s="218"/>
       <c r="Q8" s="70"/>
       <c r="R8" s="181" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
-    <row r="9" spans="2:46" ht="68.25" thickBot="1">
+    <row r="9" spans="2:46" ht="78.5" thickBot="1">
       <c r="B9" s="65" t="s">
         <v>29</v>
       </c>
       <c r="C9" s="157" t="s">
+        <v>227</v>
+      </c>
+      <c r="D9" s="157" t="s">
+        <v>212</v>
+      </c>
+      <c r="E9" s="157" t="s">
+        <v>227</v>
+      </c>
+      <c r="F9" s="157" t="s">
+        <v>227</v>
+      </c>
+      <c r="G9" s="157" t="s">
         <v>228</v>
       </c>
-      <c r="D9" s="157" t="s">
-        <v>213</v>
-      </c>
-      <c r="E9" s="157" t="s">
-        <v>228</v>
-      </c>
-      <c r="F9" s="157" t="s">
-        <v>228</v>
-      </c>
-      <c r="G9" s="157" t="s">
-        <v>229</v>
-      </c>
       <c r="H9" s="157" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="I9" s="157" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J9" s="157" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="K9" s="26" t="s">
         <v>196</v>
       </c>
       <c r="L9" s="24" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="M9" s="26" t="s">
+        <v>229</v>
+      </c>
+      <c r="N9" s="30" t="s">
         <v>230</v>
-      </c>
-      <c r="N9" s="30" t="s">
-        <v>231</v>
       </c>
       <c r="O9" s="219"/>
       <c r="P9" s="24" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="Q9" s="68"/>
       <c r="R9" s="182" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="10" spans="2:46" ht="14.25" thickTop="1">
+    <row r="10" spans="2:46" ht="13.5" thickTop="1">
       <c r="B10" s="220" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="C10" s="158" t="s">
+        <v>231</v>
+      </c>
+      <c r="D10" s="158" t="s">
+        <v>231</v>
+      </c>
+      <c r="E10" s="158" t="s">
+        <v>231</v>
+      </c>
+      <c r="F10" s="158" t="s">
+        <v>231</v>
+      </c>
+      <c r="G10" s="158" t="s">
+        <v>231</v>
+      </c>
+      <c r="H10" s="158" t="s">
+        <v>231</v>
+      </c>
+      <c r="I10" s="158" t="s">
+        <v>231</v>
+      </c>
+      <c r="J10" s="158" t="s">
+        <v>231</v>
+      </c>
+      <c r="K10" s="221" t="s">
+        <v>249</v>
+      </c>
+      <c r="L10" s="222" t="s">
         <v>232</v>
       </c>
-      <c r="D10" s="158" t="s">
-        <v>232</v>
-      </c>
-      <c r="E10" s="158" t="s">
-        <v>232</v>
-      </c>
-      <c r="F10" s="158" t="s">
-        <v>232</v>
-      </c>
-      <c r="G10" s="158" t="s">
-        <v>232</v>
-      </c>
-      <c r="H10" s="158" t="s">
-        <v>232</v>
-      </c>
-      <c r="I10" s="158" t="s">
-        <v>232</v>
-      </c>
-      <c r="J10" s="158" t="s">
-        <v>232</v>
-      </c>
-      <c r="K10" s="221" t="s">
-        <v>251</v>
-      </c>
-      <c r="L10" s="222" t="s">
+      <c r="M10" s="191" t="s">
         <v>233</v>
-      </c>
-      <c r="M10" s="191" t="s">
-        <v>234</v>
       </c>
       <c r="N10" s="192" t="s">
         <v>31</v>
@@ -55186,45 +56098,45 @@
       </c>
       <c r="Q10" s="33"/>
       <c r="R10" s="183" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="11" spans="2:46">
       <c r="B11" s="190" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C11" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D11" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E11" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F11" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G11" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H11" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I11" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J11" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K11" s="223" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="L11" s="213" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="M11" s="224" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="N11" s="199" t="s">
         <v>31</v>
@@ -55235,45 +56147,45 @@
       </c>
       <c r="Q11" s="34"/>
       <c r="R11" s="207" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="12" spans="2:46">
       <c r="B12" s="190" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="C12" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D12" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E12" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F12" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G12" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H12" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I12" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J12" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K12" s="223" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="L12" s="213" t="s">
+        <v>237</v>
+      </c>
+      <c r="M12" s="224" t="s">
         <v>238</v>
-      </c>
-      <c r="M12" s="224" t="s">
-        <v>239</v>
       </c>
       <c r="N12" s="199" t="s">
         <v>31</v>
@@ -55284,94 +56196,94 @@
       </c>
       <c r="Q12" s="34"/>
       <c r="R12" s="207" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="13" spans="2:46">
       <c r="B13" s="190" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="C13" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D13" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E13" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F13" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G13" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H13" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I13" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J13" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K13" s="223" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="L13" s="213" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="M13" s="224" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="N13" s="199" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="O13" s="159"/>
       <c r="P13" s="213" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q13" s="34"/>
       <c r="R13" s="207" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="14" spans="2:46">
       <c r="B14" s="220" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C14" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D14" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E14" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F14" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G14" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H14" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I14" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J14" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K14" s="223" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L14" s="213" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="M14" s="191" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="N14" s="199" t="s">
         <v>31</v>
@@ -55382,45 +56294,45 @@
       </c>
       <c r="Q14" s="34"/>
       <c r="R14" s="207" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="15" spans="2:46">
       <c r="B15" s="190" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="C15" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D15" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E15" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F15" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G15" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H15" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I15" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J15" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K15" s="225" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L15" s="213" t="s">
+        <v>234</v>
+      </c>
+      <c r="M15" s="224" t="s">
         <v>235</v>
-      </c>
-      <c r="M15" s="224" t="s">
-        <v>236</v>
       </c>
       <c r="N15" s="192" t="s">
         <v>31</v>
@@ -55431,45 +56343,45 @@
       </c>
       <c r="Q15" s="210"/>
       <c r="R15" s="211" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="16" spans="2:46">
       <c r="B16" s="190" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C16" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D16" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E16" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F16" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G16" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H16" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I16" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J16" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K16" s="225" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L16" s="213" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="M16" s="224" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="N16" s="199" t="s">
         <v>31</v>
@@ -55480,52 +56392,52 @@
       </c>
       <c r="Q16" s="210"/>
       <c r="R16" s="211" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="17" spans="2:46">
       <c r="B17" s="190" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="C17" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D17" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E17" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F17" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G17" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H17" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I17" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J17" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K17" s="225" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="L17" s="213" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="M17" s="224" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="N17" s="199" t="s">
         <v>199</v>
       </c>
       <c r="O17" s="197"/>
       <c r="P17" s="213" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q17" s="210"/>
       <c r="R17" s="207" t="s">
@@ -55534,40 +56446,40 @@
     </row>
     <row r="18" spans="2:46">
       <c r="B18" s="190" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="C18" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D18" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E18" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F18" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G18" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H18" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I18" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J18" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K18" s="196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="L18" s="191" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="M18" s="213" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="N18" s="199" t="s">
         <v>31</v>
@@ -55578,45 +56490,45 @@
       </c>
       <c r="Q18" s="210"/>
       <c r="R18" s="211" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="19" spans="2:46">
       <c r="B19" s="190" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="C19" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D19" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E19" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F19" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G19" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H19" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I19" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J19" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K19" s="196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="L19" s="191" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="M19" s="191" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="N19" s="199" t="s">
         <v>31</v>
@@ -55627,45 +56539,45 @@
       </c>
       <c r="Q19" s="34"/>
       <c r="R19" s="211" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="20" spans="2:46">
       <c r="B20" s="190" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C20" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D20" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E20" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F20" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G20" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H20" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I20" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J20" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K20" s="196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="L20" s="191" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="M20" s="224" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="N20" s="199" t="s">
         <v>31</v>
@@ -55676,45 +56588,45 @@
       </c>
       <c r="Q20" s="34"/>
       <c r="R20" s="211" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="21" spans="2:46">
       <c r="B21" s="190" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="C21" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D21" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E21" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F21" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G21" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H21" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I21" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J21" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K21" s="196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="L21" s="191" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="M21" s="224" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="N21" s="199" t="s">
         <v>31</v>
@@ -55725,52 +56637,52 @@
       </c>
       <c r="Q21" s="34"/>
       <c r="R21" s="211" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="22" spans="2:46">
       <c r="B22" s="190" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="C22" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D22" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E22" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F22" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G22" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H22" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I22" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J22" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K22" s="196" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="L22" s="191" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="M22" s="224" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="N22" s="199" t="s">
         <v>199</v>
       </c>
       <c r="O22" s="159"/>
       <c r="P22" s="213" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="Q22" s="34"/>
       <c r="R22" s="207" t="s">
@@ -55779,40 +56691,40 @@
     </row>
     <row r="23" spans="2:46">
       <c r="B23" s="190" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="C23" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D23" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E23" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F23" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G23" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H23" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I23" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J23" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K23" s="196" t="s">
+        <v>259</v>
+      </c>
+      <c r="L23" s="191" t="s">
         <v>261</v>
       </c>
-      <c r="L23" s="191" t="s">
-        <v>263</v>
-      </c>
       <c r="M23" s="191" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="N23" s="199" t="s">
         <v>31</v>
@@ -55823,45 +56735,45 @@
       </c>
       <c r="Q23" s="34"/>
       <c r="R23" s="211" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="24" spans="2:46">
       <c r="B24" s="190" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C24" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D24" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E24" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F24" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G24" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H24" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I24" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J24" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K24" s="196" t="s">
+        <v>259</v>
+      </c>
+      <c r="L24" s="191" t="s">
         <v>261</v>
       </c>
-      <c r="L24" s="191" t="s">
-        <v>263</v>
-      </c>
       <c r="M24" s="224" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="N24" s="199" t="s">
         <v>31</v>
@@ -55872,45 +56784,45 @@
       </c>
       <c r="Q24" s="34"/>
       <c r="R24" s="211" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="25" spans="2:46">
       <c r="B25" s="190" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="C25" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D25" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E25" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F25" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G25" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H25" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I25" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J25" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K25" s="196" t="s">
+        <v>259</v>
+      </c>
+      <c r="L25" s="191" t="s">
         <v>261</v>
       </c>
-      <c r="L25" s="191" t="s">
-        <v>263</v>
-      </c>
       <c r="M25" s="224" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="N25" s="199" t="s">
         <v>31</v>
@@ -55921,45 +56833,45 @@
       </c>
       <c r="Q25" s="34"/>
       <c r="R25" s="211" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="26" spans="2:46">
       <c r="B26" s="190" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="C26" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D26" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E26" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F26" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G26" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H26" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I26" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J26" s="159" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K26" s="196" t="s">
+        <v>259</v>
+      </c>
+      <c r="L26" s="191" t="s">
         <v>261</v>
       </c>
-      <c r="L26" s="191" t="s">
-        <v>263</v>
-      </c>
       <c r="M26" s="224" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="N26" s="241" t="s">
         <v>31</v>
@@ -55970,48 +56882,48 @@
       </c>
       <c r="Q26" s="34"/>
       <c r="R26" s="238" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
-    <row r="27" spans="2:46" ht="14.25" thickBot="1">
+    <row r="27" spans="2:46" ht="13.5" thickBot="1">
       <c r="B27" s="189" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="C27" s="197" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="D27" s="197" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="E27" s="197" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="F27" s="197" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="G27" s="197" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H27" s="197" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="I27" s="197" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="J27" s="197" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K27" s="188" t="s">
+        <v>262</v>
+      </c>
+      <c r="L27" s="209" t="s">
+        <v>263</v>
+      </c>
+      <c r="M27" s="214" t="s">
+        <v>271</v>
+      </c>
+      <c r="N27" s="228" t="s">
         <v>264</v>
-      </c>
-      <c r="L27" s="209" t="s">
-        <v>265</v>
-      </c>
-      <c r="M27" s="214" t="s">
-        <v>273</v>
-      </c>
-      <c r="N27" s="228" t="s">
-        <v>266</v>
       </c>
       <c r="O27" s="197"/>
       <c r="P27" s="214" t="s">
@@ -56019,10 +56931,10 @@
       </c>
       <c r="Q27" s="210"/>
       <c r="R27" s="211" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="V27" s="184" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="W27" s="184"/>
       <c r="X27" s="184"/>
@@ -56315,7 +57227,7 @@
       <c r="Q41" s="201"/>
       <c r="R41" s="201"/>
       <c r="V41" s="184" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="W41" s="184"/>
       <c r="X41" s="184"/>
@@ -57012,7 +57924,7 @@
     </row>
     <row r="90" spans="12:46">
       <c r="V90" s="184" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="W90" s="184"/>
       <c r="X90" s="184"/>
@@ -57064,14 +57976,14 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <sheetPr codeName="Sheet6"/>
   <dimension ref="B2:D27"/>
-  <sheetFormatPr defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultRowHeight="13"/>
   <cols>
-    <col min="2" max="2" width="4.875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.25" customWidth="1"/>
+    <col min="2" max="2" width="4.90625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.26953125" customWidth="1"/>
     <col min="4" max="4" width="86" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" ht="14.25" thickBot="1">
+    <row r="2" spans="2:4" ht="13.5" thickBot="1">
       <c r="B2" s="77" t="s">
         <v>84</v>
       </c>
@@ -57081,7 +57993,7 @@
       </c>
       <c r="D2" s="78"/>
     </row>
-    <row r="3" spans="2:4" ht="14.25" thickBot="1">
+    <row r="3" spans="2:4" ht="13.5" thickBot="1">
       <c r="B3" s="71" t="s">
         <v>84</v>
       </c>
@@ -57092,7 +58004,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="14.25" thickTop="1">
+    <row r="4" spans="2:4" ht="13.5" thickTop="1">
       <c r="B4" s="12">
         <v>0</v>
       </c>
@@ -57103,7 +58015,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="40.5">
+    <row r="5" spans="2:4" ht="39">
       <c r="B5" s="2">
         <v>1</v>
       </c>
@@ -57114,7 +58026,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="6" spans="2:4" ht="27">
+    <row r="6" spans="2:4" ht="26">
       <c r="B6" s="2">
         <v>2</v>
       </c>
@@ -57125,7 +58037,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="7" spans="2:4" ht="54">
+    <row r="7" spans="2:4" ht="52">
       <c r="B7" s="2">
         <v>3</v>
       </c>
@@ -57136,7 +58048,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="8" spans="2:4" ht="81">
+    <row r="8" spans="2:4" ht="78">
       <c r="B8" s="2">
         <v>4</v>
       </c>
@@ -57158,7 +58070,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="10" spans="2:4" ht="27">
+    <row r="10" spans="2:4" ht="26">
       <c r="B10" s="2">
         <v>6</v>
       </c>
@@ -57169,7 +58081,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="11" spans="2:4" ht="27">
+    <row r="11" spans="2:4" ht="26">
       <c r="B11" s="2">
         <v>7</v>
       </c>
@@ -57180,7 +58092,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="12" spans="2:4" ht="27">
+    <row r="12" spans="2:4" ht="26">
       <c r="B12" s="2">
         <v>8</v>
       </c>
@@ -57191,7 +58103,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="13" spans="2:4" ht="27">
+    <row r="13" spans="2:4" ht="26">
       <c r="B13" s="2">
         <v>9</v>
       </c>
@@ -57202,7 +58114,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="14" spans="2:4" ht="27">
+    <row r="14" spans="2:4" ht="26">
       <c r="B14" s="2">
         <v>10</v>
       </c>
@@ -57213,7 +58125,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="15" spans="2:4" ht="135">
+    <row r="15" spans="2:4" ht="130">
       <c r="B15" s="2">
         <v>11</v>
       </c>
@@ -57235,7 +58147,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="17" spans="2:4" ht="27">
+    <row r="17" spans="2:4" ht="26">
       <c r="B17" s="2">
         <v>13</v>
       </c>
@@ -57246,7 +58158,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="18" spans="2:4" ht="67.5">
+    <row r="18" spans="2:4" ht="91">
       <c r="B18" s="2">
         <v>14</v>
       </c>
@@ -57257,7 +58169,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="19" spans="2:4" ht="40.5">
+    <row r="19" spans="2:4" ht="39">
       <c r="B19" s="2">
         <v>15</v>
       </c>
@@ -57290,26 +58202,26 @@
         <v>189</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="27">
+    <row r="22" spans="2:4" ht="26">
       <c r="B22" s="2">
         <v>18</v>
       </c>
       <c r="C22" s="81" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D22" s="83" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
-    <row r="23" spans="2:4" ht="27">
+    <row r="23" spans="2:4" ht="26">
       <c r="B23" s="2">
         <v>19</v>
       </c>
       <c r="C23" s="81" t="s">
+        <v>277</v>
+      </c>
+      <c r="D23" s="83" t="s">
         <v>279</v>
-      </c>
-      <c r="D23" s="83" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="24" spans="2:4">
@@ -57327,7 +58239,7 @@
       <c r="C26" s="81"/>
       <c r="D26" s="67"/>
     </row>
-    <row r="27" spans="2:4" ht="14.25" thickBot="1">
+    <row r="27" spans="2:4" ht="13.5" thickBot="1">
       <c r="B27" s="3"/>
       <c r="C27" s="82"/>
       <c r="D27" s="5"/>
